--- a/data/processed/final_dataset.xlsx
+++ b/data/processed/final_dataset.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Final Dataset" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Final Dataset'!$A$1:$G$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Final Dataset'!$A$1:$H$68</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -421,88 +421,97 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="90" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="90" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Question Number</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Question ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Difficulty</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Ground Truth Final Answer</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Ground Truth Solution</t>
         </is>
       </c>
     </row>
     <row r="2" ht="54" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>ALG_E_001</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>Hendrycks</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>A box of 25 chocolate candies costs \6. How many dollars does it cost
 to buy 600 chocolate candies?</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>144</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>600 chocolate candies is (600/25) = 24 times as many candies as 25 candies. Multiplying
 the number of candies by 24 multiplies the cost by 24, so 600 candies costs 24· 6 = 144
@@ -511,37 +520,40 @@
       </c>
     </row>
     <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>ALG_E_002</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>Hendrycks</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Expand the following expression: 3(8x^2-2x+1).</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>24x^2-6x+3</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>When using the distributive property, we add the products of 3 and 8x^2, 3 and -2x, and 3
 and 1: \beginalign* 3(8x^2-2x+1) &amp;= 3· 8x^2+3· (-2x) + 3 · 1\\ &amp;= 24x^2-6x+3 \endalign*</t>
@@ -549,39 +561,42 @@
       </c>
     </row>
     <row r="4" ht="108" customHeight="1">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>ALG_M_001</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Hendrycks</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>You have a rectangular prism box with length x+5 units, width x-5
 units, and height x^2+25 units. For how many positive integer values
 of x is the volume of the box less than 700 units?</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>To find the volume of the box, we multiply the three dimensions: (x+5)(x-5)(x^2+25) =
 (x^2-25)(x^2+25) = x^4-625. We want to find x such that x^4-625&lt;700, which simplifies to
@@ -593,27 +608,30 @@
       </c>
     </row>
     <row r="5" ht="90" customHeight="1">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>ALG_M_002</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>Hendrycks</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>You have a whole pizza in the refrigerator. On your first trip to the
 refrigerator, you eat half the pizza. On each successive trip, you eat
@@ -621,12 +639,12 @@
 what fractional part of the pizza have you eaten?</t>
         </is>
       </c>
-      <c r="F5" s="1" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>\frac{31}{32}</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>On the second, third, fourth, and fifth trips, you eat \frac12^2, \frac12^3, \frac12^4,
 and \frac12^5 of the pizza, respectively. The total portion of the pizza eaten is the
@@ -637,27 +655,30 @@
       </c>
     </row>
     <row r="6" ht="144" customHeight="1">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>ALG_H_001</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
         <is>
           <t>1. Every morning Aya goes for a 9-kilometer-long walk and stops at a
 coffee shop afterwards. When she walks at a constant speed of s
@@ -669,122 +690,150 @@
 minutes spent in the coffee shop.</t>
         </is>
       </c>
-      <c r="F6" s="1" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
     </row>
     <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>ALG_H_002</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>2. There exist real numbers x and y, both greater than 1, such that
 log (yx) = x log (x4y ) = 10. Find xy. y</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
     </row>
     <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>ALG_H_003</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>7. Find the largest possible real part of 96 + 144i (75 + 117i)z + z
 where z is a complex number with ∣z∣ = 4. Here i = −1.</t>
         </is>
       </c>
-      <c r="F8" s="1" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
     </row>
     <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>ALG_H_004</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
         <is>
           <t>12. Define f(x) = ∣x∣ − 1 and g(x) = ∣x∣ − 1. Find the number of
 intersections of 2 4 the graphs of y = 4g(f(sin(2πx))) and x =
 4g(f(cos(3πy))).</t>
         </is>
       </c>
-      <c r="F9" s="1" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
     </row>
     <row r="10" ht="72" customHeight="1">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>ALG_H_005</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
         <is>
           <t>4. Let x,y, and z be positive real numbers that satisfy the following
 system of equations: x 1 log = 2 (yz ) 2 y 1 log = 2 (xz ) 3 z 1 log =
@@ -792,93 +841,114 @@
 relatively prime positive 2 n integers. Find m + n.</t>
         </is>
       </c>
-      <c r="F10" s="1" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
     </row>
     <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>ALG_H_006</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
         <is>
           <t>11. Find the number of triples of nonnegative integers (a,b,c)
 satisfying a + b + c = 300 and a2b + a2c + b2a + b2c + c2a + c2b =
 6,000,000.</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
     </row>
     <row r="12" ht="54" customHeight="1">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>ALG_H_007</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
         <is>
           <t>4. Find the number of ordered pairs (x,y), where both x and y are
 integers between −100 and 100, inclusive, such that 12x2 − xy − 6y2 =
 0.</t>
         </is>
       </c>
-      <c r="F12" s="1" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
     </row>
     <row r="13" ht="72" customHeight="1">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
         <is>
           <t>ALG_H_008</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
         <is>
           <t>4. The product 63 log (5k2−1) k ∏ log (5k2−4) k+1 k=4 log (515) 4 =
 log (512) 5 log (524) ⋅ 5 log (521) 6 log (535) ⋅ 6 log (532) 7 log
@@ -886,62 +956,76 @@
 relatively prime positive integers. Find m + n. n</t>
         </is>
       </c>
-      <c r="F13" s="1" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
     </row>
     <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>ALG_H_009</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
         <is>
           <t>9. There are n values of x in the interval 0 &lt; x &lt; 2π where f(x) =
 sin(7π ⋅ sin(5x)) = 0. For t of these n values of x, the graph of y =
 f(x) is tangent to the x-axis. Find n + t.</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
     </row>
     <row r="15" ht="72" customHeight="1">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t>ALG_H_010</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
         <is>
           <t>13. Let the sequence of rationals x,x,… be defined such that x = 25
 and 1 2 1 11 1 1 x = x + − 1 k+1 k 3 ( x ) k for all k ≥ 1. Then x can
@@ -949,31 +1033,38 @@
 n. Find the remainder when m + n is divided by 1000.</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
     </row>
     <row r="16" ht="72" customHeight="1">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
         <is>
           <t>ALG_H_011</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
         <is>
           <t>15. There are exactly three positive real numbers k such that the
 function f(x) (x−18)(x−72)(x−98)(x−k) = x defined over the positive
@@ -981,31 +1072,38 @@
 numbers x. Find the sum of these three values of k.</t>
         </is>
       </c>
-      <c r="F16" s="1" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
     </row>
     <row r="17" ht="180" customHeight="1">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t>ALG_H_012</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
         <is>
           <t>1. Patrick started walking at a constant speed along a straight road
 from his school to the park. One hour after Patrick left, Tanya
@@ -1019,124 +1117,152 @@
 integers. Find n m + n.</t>
         </is>
       </c>
-      <c r="F17" s="1" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
     </row>
     <row r="18" ht="54" customHeight="1">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
         <is>
           <t>ALG_H_013</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D18" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
         <is>
           <t>6. The product of all positive real numbers x satisfying the equation
 20 xlog x = 26x 2026 is an integer P. Find the number of positive
 integer divisors of P.</t>
         </is>
       </c>
-      <c r="F18" s="1" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
     </row>
     <row r="19" ht="54" customHeight="1">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
         <is>
           <t>ALG_H_014</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D19" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
         <is>
           <t>1. Find the sum of the 10th terms of all arithmetic sequences of
 integers that have first term equal to 4 and include both 24 and 34 as
 terms.</t>
         </is>
       </c>
-      <c r="F19" s="1" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
     </row>
     <row r="20" ht="54" customHeight="1">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t>ALG_H_015</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
         <is>
           <t>9. Let S denote the value of the infinite sum 1 1 1 1 + + + + ⋯ 9 99
 999 9999 Find the remainder when the greatest integer less than or
 equal to 10100S is divided by 1000.</t>
         </is>
       </c>
-      <c r="F20" s="1" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
     </row>
     <row r="21" ht="72" customHeight="1">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
         <is>
           <t>ALG_H_016</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
           <t>Algebra</t>
         </is>
       </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
         <is>
           <t>11. Find the greatest integer n such that the cubic polynomial n x3 −
 x2 + (n − 11)x − 400 6 has roots α2,β2, and γ2, where α,β, and γ are
@@ -1144,31 +1270,38 @@
 for α + β + γ.</t>
         </is>
       </c>
-      <c r="F21" s="1" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
+      <c r="G21" s="1" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
     </row>
     <row r="22" ht="72" customHeight="1">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
         <is>
           <t>NT_E_001</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>Hendrycks</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="D22" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="D22" s="1" t="inlineStr">
+      <c r="E22" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="F22" s="1" t="inlineStr">
         <is>
           <t>A bag of grapes is to be distributed evenly to 5 kids in a class, and
 the grapes that are left over will be thrown out. If each student
@@ -1176,12 +1309,12 @@
 possible number of grapes that could be thrown out?</t>
         </is>
       </c>
-      <c r="F22" s="1" t="inlineStr">
+      <c r="G22" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>If we have at least 5 grapes left, we can give each student one more, so they do not have
 the greatest possible number. On the other hand, if we have 4 grapes left, we cannot give
@@ -1191,39 +1324,42 @@
       </c>
     </row>
     <row r="23" ht="54" customHeight="1">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
         <is>
           <t>NT_E_002</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>Hendrycks</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="D23" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="E23" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="F23" s="1" t="inlineStr">
         <is>
           <t>Fifty cards, numbered 1-50, are placed in a box. One card is randomly
 selected. What is the probability that the number on the card is prime
 and is a multiple of 7? Express your answer as a common fraction.</t>
         </is>
       </c>
-      <c r="F23" s="1" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
         <is>
           <t>\frac{1}{50}</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>The only multiple of 7 that is prime is 7. Any other multiple of 7 has at least three
 positive divisors: 1, 7, and itself. Therefore, the probability that the selected number
@@ -1232,38 +1368,41 @@
       </c>
     </row>
     <row r="24" ht="108" customHeight="1">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
         <is>
           <t>NT_M_001</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>Hendrycks</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="D24" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="D24" s="1" t="inlineStr">
+      <c r="E24" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="F24" s="1" t="inlineStr">
         <is>
           <t>Find the arithmetic mean of the reciprocals of the first three prime
 numbers.</t>
         </is>
       </c>
-      <c r="F24" s="1" t="inlineStr">
+      <c r="G24" s="1" t="inlineStr">
         <is>
           <t>\frac{31}{90}</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>The first three prime numbers are 2, 3, and 5, and their reciprocals are 1/2, 1/3, and 1/5
 respectively. To find the mean of these three numbers, we must first find their sum and
@@ -1275,38 +1414,41 @@
       </c>
     </row>
     <row r="25" ht="72" customHeight="1">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
         <is>
           <t>NT_M_002</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>Hendrycks</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="D25" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="D25" s="1" t="inlineStr">
+      <c r="E25" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="F25" s="1" t="inlineStr">
         <is>
           <t>If the 25th day of the year 2003 falls on a Saturday, on what day of
 the week did the 284th day of the year 2003 fall?</t>
         </is>
       </c>
-      <c r="F25" s="1" t="inlineStr">
+      <c r="G25" s="1" t="inlineStr">
         <is>
           <t>\text{Saturday}</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>There are 7 days in a week. Two days of the year fall on the same day of the week if and
 only if they are congruent modulo 7. Notice that \[284\equiv4\pmod7\] and
@@ -1316,58 +1458,68 @@
       </c>
     </row>
     <row r="26" ht="54" customHeight="1">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
         <is>
           <t>NT_H_001</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="inlineStr">
         <is>
           <t>13. Let p be the least prime number for which there exists an integer
 n such that n4 + 1 is divisible by p2. Find the least positive integer
 m such that m4 + 1 is divisible by p2.</t>
         </is>
       </c>
-      <c r="F26" s="1" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="G26" s="1" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
     </row>
     <row r="27" ht="72" customHeight="1">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
         <is>
           <t>NT_H_002</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
         <is>
           <t>7. Let N be the greatest four-digit integer with the property that
 whenever one of its digits is changed to 1, the resulting number is
@@ -1375,61 +1527,75 @@
 respectively, when N is divided by 1000. Find Q + R.</t>
         </is>
       </c>
-      <c r="F27" s="1" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>699</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
     </row>
     <row r="28" ht="36" customHeight="1">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
         <is>
           <t>NT_H_003</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="inlineStr">
         <is>
           <t>13. Let ω = 1 be a 13th root of unity. Find the remainder when 12 (2
 − 2ωk + ω2k ) ∏ k=0 is divided by 1000.</t>
         </is>
       </c>
-      <c r="F28" s="1" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
     </row>
     <row r="29" ht="90" customHeight="1">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
         <is>
           <t>NT_H_004</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
         <is>
           <t>14. Let b ≥ 2 be an integer. Call a positive integer nb-eautiful if it
 has exactly two digits when expressed in base b and these two digits
@@ -1438,61 +1604,75 @@
 b-eautiful integers.</t>
         </is>
       </c>
-      <c r="F29" s="1" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
     </row>
     <row r="30" ht="36" customHeight="1">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
         <is>
           <t>NT_H_005</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="D30" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F30" s="1" t="inlineStr">
         <is>
           <t>1. Find the sum of all integer bases b &gt; 9 for which 17 is a divisor
 of 97. b b</t>
         </is>
       </c>
-      <c r="F30" s="1" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
     </row>
     <row r="31" ht="72" customHeight="1">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
         <is>
           <t>NT_H_006</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="inlineStr">
+        <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F31" s="1" t="inlineStr">
         <is>
           <t>5. There are 8! = 40320 eight-digit positive integers that use each of
 the digits 1,2,3,4,5,6,7,8 exactly once. Let N be the number of these
@@ -1500,154 +1680,189 @@
 2025.</t>
         </is>
       </c>
-      <c r="F31" s="1" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
+      <c r="G31" s="1" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
     </row>
     <row r="32" ht="54" customHeight="1">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
         <is>
           <t>NT_H_007</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="D32" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="inlineStr">
         <is>
           <t>15. Let N denote the number of ordered triples of positive integers
 (a,b,c) such that a,b,c ≤ 36 and a3 + b3 + c3 is a multiple of 37.
 Find the remainder when N is divided by 1000.</t>
         </is>
       </c>
-      <c r="F32" s="1" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t>735</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
     </row>
     <row r="33" ht="36" customHeight="1">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
         <is>
           <t>NT_H_008</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="inlineStr">
+        <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="D33" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F33" s="1" t="inlineStr">
         <is>
           <t>2. Find the sum of all positive integers n such that n + 2 divides the
 product 3(n + 3)(n2 + 9).</t>
         </is>
       </c>
-      <c r="F33" s="1" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr"/>
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
     </row>
     <row r="34" ht="54" customHeight="1">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
         <is>
           <t>NT_H_009</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="inlineStr">
+        <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="inlineStr">
         <is>
           <t>4. Find the number of integers less than or equal to 100 that are
 equal to a + b + ab for some choice of distinct positive integers a
 and b.</t>
         </is>
       </c>
-      <c r="F34" s="1" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
     </row>
     <row r="35" ht="54" customHeight="1">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
         <is>
           <t>NT_H_010</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="inlineStr">
+        <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F35" s="1" t="inlineStr">
         <is>
           <t>8. Let N be the number of positive integer divisors of 1701717 that
 leave a remainder of 5 upon division by 12. Find the remainder when N
 is divided by 1000.</t>
         </is>
       </c>
-      <c r="F35" s="1" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr"/>
+      <c r="G35" s="1" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
     </row>
     <row r="36" ht="90" customHeight="1">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
         <is>
           <t>NT_H_011</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="inlineStr">
+        <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F36" s="1" t="inlineStr">
         <is>
           <t>4. For each positive integer n let f(n) be the value of the base-ten
 numeral n viewed in base b, where b is the least integer greater than
@@ -1656,43 +1871,50 @@
 the number of positive integers n less than 1000 such that f(n) = n.</t>
         </is>
       </c>
-      <c r="F36" s="1" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
+      <c r="G36" s="1" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
     </row>
     <row r="37" ht="54" customHeight="1">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="A37" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
         <is>
           <t>PROB_E_001</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>Hendrycks</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="D37" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="D37" s="1" t="inlineStr">
+      <c r="E37" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="F37" s="1" t="inlineStr">
         <is>
           <t>A bag has 3 red marbles and 5 white marbles. Two marbles are drawn
 from the bag and not replaced. What is the probability that the first
 marble is red and the second marble is white?</t>
         </is>
       </c>
-      <c r="F37" s="1" t="inlineStr">
+      <c r="G37" s="1" t="inlineStr">
         <is>
           <t>\dfrac{15}{56}</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>The probability that the first is red is \dfrac38. Now with 7 remaining, the probability
 that the second is white is \dfrac57. The answer is \dfrac38 × \dfrac57 = \dfrac1556.</t>
@@ -1700,27 +1922,30 @@
       </c>
     </row>
     <row r="38" ht="108" customHeight="1">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="A38" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
         <is>
           <t>PROB_E_002</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>Hendrycks</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="D38" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="D38" s="1" t="inlineStr">
+      <c r="E38" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="F38" s="1" t="inlineStr">
         <is>
           <t>A board game spinner is divided into four regions labeled A, B, C, and
 D. The probability of the arrow stopping on region A is (3/8), the
@@ -1730,12 +1955,12 @@
 Express your answer as a common fraction.</t>
         </is>
       </c>
-      <c r="F38" s="1" t="inlineStr">
+      <c r="G38" s="1" t="inlineStr">
         <is>
           <t>\frac{3}{16}</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Let x be the probability that we want. Since the sum of the four probabilities is 1, we
 have the equation 1 = (3/8) + (1/4) + x + x = (5/8) + 2x. Solving the equation 1=(5/8) +
@@ -1744,39 +1969,42 @@
       </c>
     </row>
     <row r="39" ht="126" customHeight="1">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
         <is>
           <t>PROB_M_001</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>Hendrycks</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="D39" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="D39" s="1" t="inlineStr">
+      <c r="E39" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="F39" s="1" t="inlineStr">
         <is>
           <t>Two different integers are randomly chosen from the set \ -5, -8, 7,
 4, -2 \. What is the probability that their product is negative?
 Express your answer as a common fraction.</t>
         </is>
       </c>
-      <c r="F39" s="1" t="inlineStr">
+      <c r="G39" s="1" t="inlineStr">
         <is>
           <t>\frac{3}{5}</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>We don't consider the order that we choose integers in this problem, meaning that choosing
 a -5 and then a -8 is the same as choosing a -8 and then a -5. The product of two integers
@@ -1789,38 +2017,41 @@
       </c>
     </row>
     <row r="40" ht="54" customHeight="1">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="A40" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
         <is>
           <t>PROB_M_002</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>Hendrycks</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="D40" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="D40" s="1" t="inlineStr">
+      <c r="E40" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="F40" s="1" t="inlineStr">
         <is>
           <t>Two standard 6-sided dice are rolled. What is the probability that the
 sum rolled is a perfect square?</t>
         </is>
       </c>
-      <c r="F40" s="1" t="inlineStr">
+      <c r="G40" s="1" t="inlineStr">
         <is>
           <t>\dfrac{7}{36}</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Rolling two dice has 6 × 6=36 possible outcomes. The only perfect squares that we can roll
 are 4 and 9. Pairs adding up to 4 are 1+3, 2+2, and 3+1. Those that add up to 9 are 3+6,
@@ -1829,27 +2060,30 @@
       </c>
     </row>
     <row r="41" ht="108" customHeight="1">
-      <c r="A41" s="1" t="inlineStr">
+      <c r="A41" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
         <is>
           <t>PROB_H_001</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="inlineStr">
+        <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F41" s="1" t="inlineStr">
         <is>
           <t>4. Jen enters a lottery by selecting 4 distinct elements of S =
 {1,2,3,…,9,10}. Then four elements of S are drawn at random. Jen wins
@@ -1859,31 +2093,38 @@
 are relatively prime positive integers. Find m + n.</t>
         </is>
       </c>
-      <c r="F41" s="1" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
+      <c r="G41" s="1" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
     </row>
     <row r="42" ht="90" customHeight="1">
-      <c r="A42" s="1" t="inlineStr">
+      <c r="A42" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
         <is>
           <t>PROB_H_002</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E42" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F42" s="1" t="inlineStr">
         <is>
           <t>11. Each vertex of a regular octagon is independently colored either
 red or blue with equal probability. The probability that the octagon
@@ -1892,31 +2133,38 @@
 relatively prime positive integers. Find m + n.</t>
         </is>
       </c>
-      <c r="F42" s="1" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
+      <c r="G42" s="1" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
     </row>
     <row r="43" ht="126" customHeight="1">
-      <c r="A43" s="1" t="inlineStr">
+      <c r="A43" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
         <is>
           <t>PROB_H_003</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F43" s="1" t="inlineStr">
         <is>
           <t>7. The twelve letters A,B,C,D,E,F,G,H,I,J,K, and L are randomly
 grouped into six pairs of letters. The two letters in each pair are
@@ -1927,31 +2175,38 @@
 prime positive integers. Find m + n.</t>
         </is>
       </c>
-      <c r="F43" s="1" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr"/>
+      <c r="G43" s="1" t="inlineStr">
+        <is>
+          <t>821</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
     </row>
     <row r="44" ht="108" customHeight="1">
-      <c r="A44" s="1" t="inlineStr">
+      <c r="A44" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
         <is>
           <t>PROB_H_004</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="inlineStr">
+        <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E44" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F44" s="1" t="inlineStr">
         <is>
           <t>13. Alex divides a disk into four quadrants with two perpendicular
 diameters intersecting at the center of the disk. He draws 25 more
@@ -1961,31 +2216,38 @@
 into which these 27 line segments divide the disk.</t>
         </is>
       </c>
-      <c r="F44" s="1" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr"/>
+      <c r="G44" s="1" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
     </row>
     <row r="45" ht="90" customHeight="1">
-      <c r="A45" s="1" t="inlineStr">
+      <c r="A45" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
         <is>
           <t>PROB_H_005</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="inlineStr">
+        <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E45" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F45" s="1" t="inlineStr">
         <is>
           <t>7. Let A be the set of positive integer divisors of 2025. Let B be a
 randomly selected subset of A. The probability that B is a nonempty
@@ -1994,31 +2256,38 @@
 Find m + n.</t>
         </is>
       </c>
-      <c r="F45" s="1" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr"/>
+      <c r="G45" s="1" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr"/>
     </row>
     <row r="46" ht="198" customHeight="1">
-      <c r="A46" s="1" t="inlineStr">
+      <c r="A46" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
         <is>
           <t>PROB_H_006</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="inlineStr">
+        <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E46" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F46" s="1" t="inlineStr">
         <is>
           <t>9. Joanne has a blank fair six-sided die and six stickers each
 displaying a different integer from 1 to 6. Joanne rolls the die and
@@ -2033,31 +2302,38 @@
 relatively prime positive integers. n Find m + n.</t>
         </is>
       </c>
-      <c r="F46" s="1" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr"/>
+      <c r="G46" s="1" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
     </row>
     <row r="47" ht="108" customHeight="1">
-      <c r="A47" s="1" t="inlineStr">
+      <c r="A47" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="1" t="inlineStr">
         <is>
           <t>PROB_H_007</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="inlineStr">
+        <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="D47" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F47" s="1" t="inlineStr">
         <is>
           <t>5. An urn contains n marbles. Each marble is either red or blue, and
 there are at least 7 marbles of each color. When 7 marbles are drawn
@@ -2067,31 +2343,38 @@
 this is possible.</t>
         </is>
       </c>
-      <c r="F47" s="1" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
+      <c r="G47" s="1" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
     </row>
     <row r="48" ht="108" customHeight="1">
-      <c r="A48" s="1" t="inlineStr">
+      <c r="A48" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
         <is>
           <t>PROB_H_008</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="inlineStr">
+        <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E48" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F48" s="1" t="inlineStr">
         <is>
           <t>7. A standard fair six-sided die is rolled repeatedly. Each time the
 die reads 1 or 2, Alice gets a coin; each time it reads 3 or 4, Bob
@@ -2101,42 +2384,49 @@
 relatively n prime positive integers. Find 100m + n.</t>
         </is>
       </c>
-      <c r="F48" s="1" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="G48" s="1" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
     </row>
     <row r="49" ht="54" customHeight="1">
-      <c r="A49" s="1" t="inlineStr">
+      <c r="A49" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
         <is>
           <t>COMB_E_001</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>Hendrycks</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="D49" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="D49" s="1" t="inlineStr">
+      <c r="E49" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="F49" s="1" t="inlineStr">
         <is>
           <t>Determine the number of ways to arrange the letters of the word
 ALABAMA.</t>
         </is>
       </c>
-      <c r="F49" s="1" t="inlineStr">
+      <c r="G49" s="1" t="inlineStr">
         <is>
           <t>210</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>First we count the arrangements if the four A's are unique, which is 7!. Then since the
 A's are not unique, we divide by 4! for the arrangements of A, for an answer of \dfrac7!4!
@@ -2145,38 +2435,41 @@
       </c>
     </row>
     <row r="50" ht="54" customHeight="1">
-      <c r="A50" s="1" t="inlineStr">
+      <c r="A50" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="1" t="inlineStr">
         <is>
           <t>COMB_E_002</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>Hendrycks</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="D50" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="D50" s="1" t="inlineStr">
+      <c r="E50" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="F50" s="1" t="inlineStr">
         <is>
           <t>From a group of six students, how many different four-student
 committees can be chosen?</t>
         </is>
       </c>
-      <c r="F50" s="1" t="inlineStr">
+      <c r="G50" s="1" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>There are \binomnk=(n!/k!(n-k)!) ways to choose k objects from a group of n distinct
 objects, so \binom64=(6!/4!2!)=(6·5/2)=15 four-member committees may be formed from a
@@ -2185,38 +2478,41 @@
       </c>
     </row>
     <row r="51" ht="54" customHeight="1">
-      <c r="A51" s="1" t="inlineStr">
+      <c r="A51" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1" t="inlineStr">
         <is>
           <t>COMB_M_001</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>Hendrycks</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="D51" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="D51" s="1" t="inlineStr">
+      <c r="E51" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="F51" s="1" t="inlineStr">
         <is>
           <t>Using only the digits 7, 8 and 9, how many positive seven-digit
 integers can be made that are palindromes?</t>
         </is>
       </c>
-      <c r="F51" s="1" t="inlineStr">
+      <c r="G51" s="1" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>Since we need to make a palindrome, it only matters what we pick for the first 4 digits,
 since the other three are reflections of the first three. Therefore, since each of them
@@ -2225,27 +2521,30 @@
       </c>
     </row>
     <row r="52" ht="180" customHeight="1">
-      <c r="A52" s="1" t="inlineStr">
+      <c r="A52" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1" t="inlineStr">
         <is>
           <t>COMB_M_002</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>Hendrycks</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="D52" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="D52" s="1" t="inlineStr">
+      <c r="E52" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="F52" s="1" t="inlineStr">
         <is>
           <t>You have 5 red shirts, 5 green shirts, 6 pairs of pants, 8 green hats
 and 8 red hats, all of which are distinct. How many outfits can you
@@ -2253,12 +2552,12 @@
 having the same color of shirts and hats?</t>
         </is>
       </c>
-      <c r="F52" s="1" t="inlineStr">
+      <c r="G52" s="1" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Consider two cases: \bullet Case 1: the person wears a red shirt and a green hat. There
 are 5 options for shirts, 6 options for pants, and 8 options for hats, for a total of 5 ×
@@ -2274,27 +2573,30 @@
       </c>
     </row>
     <row r="53" ht="108" customHeight="1">
-      <c r="A53" s="1" t="inlineStr">
+      <c r="A53" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="1" t="inlineStr">
         <is>
           <t>COMB_H_001</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="inlineStr">
+        <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E53" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F53" s="1" t="inlineStr">
         <is>
           <t>3. Alice and Bob play the following game. A stack of n tokens lies
 before them. The players take turns with Alice going first. On each
@@ -2304,31 +2606,38 @@
 that guarantees that Bob wins, regardless of Alice's moves.</t>
         </is>
       </c>
-      <c r="F53" s="1" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr"/>
+      <c r="G53" s="1" t="inlineStr">
+        <is>
+          <t>809</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr"/>
     </row>
     <row r="54" ht="108" customHeight="1">
-      <c r="A54" s="1" t="inlineStr">
+      <c r="A54" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="1" t="inlineStr">
         <is>
           <t>COMB_H_002</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="inlineStr">
+        <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E54" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F54" s="1" t="inlineStr">
         <is>
           <t>1. Among the 900 residents of Aimeville, there are 195 who own a
 diamond ring, 367 who own a set of golf clubs, and 562 who own a
@@ -2338,31 +2647,38 @@
 the number of residents of Aimeville who own all four of these things.</t>
         </is>
       </c>
-      <c r="F54" s="1" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
+      <c r="G54" s="1" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr"/>
     </row>
     <row r="55" ht="90" customHeight="1">
-      <c r="A55" s="1" t="inlineStr">
+      <c r="A55" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1" t="inlineStr">
         <is>
           <t>COMB_H_003</t>
         </is>
       </c>
-      <c r="B55" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D55" s="1" t="inlineStr">
+        <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="D55" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E55" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F55" s="1" t="inlineStr">
         <is>
           <t>2. A list of positive integers has the following properties: • The sum
 of the items in the list is 30. • The unique mode of the list is 9. •
@@ -2371,31 +2687,38 @@
 list.</t>
         </is>
       </c>
-      <c r="F55" s="1" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr"/>
+      <c r="G55" s="1" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr"/>
     </row>
     <row r="56" ht="72" customHeight="1">
-      <c r="A56" s="1" t="inlineStr">
+      <c r="A56" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
         <is>
           <t>COMB_H_004</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="inlineStr">
+        <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E56" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F56" s="1" t="inlineStr">
         <is>
           <t>6. Alice chooses a set A of positive integers. Then Bob lists all
 finite nonempty sets B of positive integers with the property that the
@@ -2403,31 +2726,38 @@
 sum of the elements of A.</t>
         </is>
       </c>
-      <c r="F56" s="1" t="inlineStr"/>
-      <c r="G56" s="2" t="inlineStr"/>
+      <c r="G56" s="1" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr"/>
     </row>
     <row r="57" ht="108" customHeight="1">
-      <c r="A57" s="1" t="inlineStr">
+      <c r="A57" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="1" t="inlineStr">
         <is>
           <t>COMB_H_005</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="inlineStr">
+        <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E57" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F57" s="1" t="inlineStr">
         <is>
           <t>9. There is a collection of 25 indistinguishable white chips and 25
 indistinguishable black chips. Find the number of ways to place some
@@ -2437,31 +2767,38 @@
 would violate one or more of the previous two conditions.</t>
         </is>
       </c>
-      <c r="F57" s="1" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
+      <c r="G57" s="1" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr"/>
     </row>
     <row r="58" ht="144" customHeight="1">
-      <c r="A58" s="1" t="inlineStr">
+      <c r="A58" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="1" t="inlineStr">
         <is>
           <t>COMB_H_006</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D58" s="1" t="inlineStr">
+        <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E58" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F58" s="1" t="inlineStr">
         <is>
           <t>3. The 9 members of a baseball team went to an ice-cream parlor after
 their game. Each player had a single scoop cone of chocolate, vanilla,
@@ -2473,31 +2810,38 @@
 remainder when N is divided by 1000.</t>
         </is>
       </c>
-      <c r="F58" s="1" t="inlineStr"/>
-      <c r="G58" s="2" t="inlineStr"/>
+      <c r="G58" s="1" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
     </row>
     <row r="59" ht="270" customHeight="1">
-      <c r="A59" s="1" t="inlineStr">
+      <c r="A59" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="1" t="inlineStr">
         <is>
           <t>COMB_H_007</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D59" s="1" t="inlineStr">
+        <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E59" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F59" s="1" t="inlineStr">
         <is>
           <t>8. From an unlimited supply of 1-cent coins, 10-cent coins, and
 25-cent coins, Silas wants to find a collection of coins that has a
@@ -2516,31 +2860,38 @@
 algorithm succeeds.</t>
         </is>
       </c>
-      <c r="F59" s="1" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr"/>
+      <c r="G59" s="1" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr"/>
     </row>
     <row r="60" ht="72" customHeight="1">
-      <c r="A60" s="1" t="inlineStr">
+      <c r="A60" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="1" t="inlineStr">
         <is>
           <t>COMB_H_008</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D60" s="1" t="inlineStr">
+        <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E60" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F60" s="1" t="inlineStr">
         <is>
           <t>10. Sixteen chairs are arranged in a row. Eight people each select a
 chair in which to sit so that no person sits next to two other people.
@@ -2548,62 +2899,76 @@
 Find the remainder when N is divided by 1000.</t>
         </is>
       </c>
-      <c r="F60" s="1" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr"/>
+      <c r="G60" s="1" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
     </row>
     <row r="61" ht="54" customHeight="1">
-      <c r="A61" s="1" t="inlineStr">
+      <c r="A61" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="1" t="inlineStr">
         <is>
           <t>COMB_H_009</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D61" s="1" t="inlineStr">
+        <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E61" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F61" s="1" t="inlineStr">
         <is>
           <t>11. Let S be the set of vertices of a regular 24-gon. Find the number
 of ways to draw 12 segments of equal lengths so that each vertex in S
 is an endpoint of exactly one of the 12 segments.</t>
         </is>
       </c>
-      <c r="F61" s="1" t="inlineStr"/>
-      <c r="G61" s="2" t="inlineStr"/>
+      <c r="G61" s="1" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr"/>
     </row>
     <row r="62" ht="90" customHeight="1">
-      <c r="A62" s="1" t="inlineStr">
+      <c r="A62" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="1" t="inlineStr">
         <is>
           <t>COMB_H_010</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D62" s="1" t="inlineStr">
+        <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="D62" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E62" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F62" s="1" t="inlineStr">
         <is>
           <t>2. Find the number of positive integer palindromes written in base 10,
 with no zero digits, and whose digits add up to 13. For example, 42124
@@ -2612,61 +2977,75 @@
 left.</t>
         </is>
       </c>
-      <c r="F62" s="1" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr"/>
+      <c r="G62" s="1" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr"/>
     </row>
     <row r="63" ht="36" customHeight="1">
-      <c r="A63" s="1" t="inlineStr">
+      <c r="A63" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="1" t="inlineStr">
         <is>
           <t>COMB_H_011</t>
         </is>
       </c>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D63" s="1" t="inlineStr">
+        <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="D63" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E63" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F63" s="1" t="inlineStr">
         <is>
           <t>7. Find the number of functions π mapping the set A = {1,2,3,4,5,6}
 onto A such that for every a ∈ A, π(π(π(π(π(π(a)))))) = a.</t>
         </is>
       </c>
-      <c r="F63" s="1" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr"/>
+      <c r="G63" s="1" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr"/>
     </row>
     <row r="64" ht="108" customHeight="1">
-      <c r="A64" s="1" t="inlineStr">
+      <c r="A64" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="1" t="inlineStr">
         <is>
           <t>COMB_H_012</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D64" s="1" t="inlineStr">
+        <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E64" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F64" s="1" t="inlineStr">
         <is>
           <t>11. The integers from 1 to 64 are placed in some order into an 8 × 8
 grid of cells with one number in each cell. Let a be the number placed
@@ -2676,31 +3055,38 @@
 the maximum possible value of M is divided by 1000.</t>
         </is>
       </c>
-      <c r="F64" s="1" t="inlineStr"/>
-      <c r="G64" s="2" t="inlineStr"/>
+      <c r="G64" s="1" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr"/>
     </row>
     <row r="65" ht="108" customHeight="1">
-      <c r="A65" s="1" t="inlineStr">
+      <c r="A65" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="1" t="inlineStr">
         <is>
           <t>COMB_H_013</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D65" s="1" t="inlineStr">
+        <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E65" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F65" s="1" t="inlineStr">
         <is>
           <t>13. For each nonnegative integer r less than 502 define 10,000 S =, r
 ∑ (502m + r) m≥0 where ( 10,000 ) is defined to be 0 when n &gt; 10,000.
@@ -2710,31 +3096,38 @@
 of the 0 1 2 501 prime number 503.</t>
         </is>
       </c>
-      <c r="F65" s="1" t="inlineStr"/>
-      <c r="G65" s="2" t="inlineStr"/>
+      <c r="G65" s="1" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr"/>
     </row>
     <row r="66" ht="108" customHeight="1">
-      <c r="A66" s="1" t="inlineStr">
+      <c r="A66" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="1" t="inlineStr">
         <is>
           <t>COMB_H_014</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D66" s="1" t="inlineStr">
+        <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E66" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F66" s="1" t="inlineStr">
         <is>
           <t>13. Call finite sets of integers S and T cousins if • S and T have the
 same number of elements, • S and T are disjoint, and • the elements of
@@ -2744,31 +3137,38 @@
 least number of elements the set S can have.</t>
         </is>
       </c>
-      <c r="F66" s="1" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr"/>
+      <c r="G66" s="1" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr"/>
     </row>
     <row r="67" ht="90" customHeight="1">
-      <c r="A67" s="1" t="inlineStr">
+      <c r="A67" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="1" t="inlineStr">
         <is>
           <t>COMB_H_015</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D67" s="1" t="inlineStr">
+        <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E67" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F67" s="1" t="inlineStr">
         <is>
           <t>14. For integers a and b, let a ∘ b = a − b if a is odd and b is even,
 and a ∘ b = a + b otherwise. Find the number of sequences a,a,a,…,a of
@@ -2777,31 +3177,38 @@
 left to right; that is, a ∘ a ∘ a means 1 2 3 (a ∘ a ) ∘ a. 1 2 3</t>
         </is>
       </c>
-      <c r="F67" s="1" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr"/>
+      <c r="G67" s="1" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr"/>
     </row>
     <row r="68" ht="90" customHeight="1">
-      <c r="A68" s="1" t="inlineStr">
+      <c r="A68" s="1" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="1" t="inlineStr">
         <is>
           <t>COMB_H_016</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D68" s="1" t="inlineStr">
+        <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="D68" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E68" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F68" s="1" t="inlineStr">
         <is>
           <t>15. Find the number of ordered 7−tuples (a,a,a,…,a ) having the
 following 1 2 3 7 properties: • a ∈ {1,2,3} for all k. k • a + a + a +
@@ -2810,11 +3217,15 @@
 5 7 5 6 1 6 7 2 7 1 3 3.</t>
         </is>
       </c>
-      <c r="F68" s="1" t="inlineStr"/>
-      <c r="G68" s="2" t="inlineStr"/>
+      <c r="G68" s="1" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G68"/>
+  <autoFilter ref="A1:H68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/processed/final_dataset.xlsx
+++ b/data/processed/final_dataset.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Final Dataset" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Final Dataset'!$A$1:$H$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Final Dataset'!$A$1:$H$132</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -48,11 +48,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -421,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H121"/>
+  <dimension ref="A1:H132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -470,7 +467,7 @@
           <t>Ground Truth Final Answer</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Ground Truth Solution</t>
         </is>
@@ -510,7 +507,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>Since 81 = 3^4, we have \[3^m = (81)^\frac12 = (3^4)^\frac12 = 3^4· \frac12 = 3^2,\] which
 means m=2.</t>
@@ -551,7 +548,7 @@
           <t>625</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>We note that 361=19^2 and 36=6^2, so x=19^2+2(19)(6)+6^2. This is just the binomial
 expansion of (19+6)^2=25^2=625.</t>
@@ -592,7 +589,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>We want to write everything in terms of powers of 3. Doing so gives us 3^n = 3 · (3^2)^3 ·
 (3^4)^2. This simplifies to 3^n = 3 · 3^6 · 3^8, so 3^n = 3^15. Therefore, n = 15.</t>
@@ -635,7 +632,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="1" t="inlineStr">
         <is>
           <t>If you call the number of bounces b, then this problem can be phrased as: what is the
 minimum b, such that 243· ((2/3))^b &lt; 30 arrow ((2/3))^b &lt; (30/243), at which point you
@@ -681,7 +678,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="1" t="inlineStr">
         <is>
           <t>We have a geometric sequence with first term 10 and common ratio 1/2. Any term in this
 sequence can be represented as 10·((1/2))^k, where k is the number of bounces (for
@@ -727,7 +724,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="1" t="inlineStr">
         <is>
           <t>We have a geometric sequence with first term 1000 and common ratio 1/2. Any term in this
 sequence can be represented as 1000·((1/2))^k, where k is the number of bounces (for
@@ -772,7 +769,7 @@
           <t>144</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="1" t="inlineStr">
         <is>
           <t>600 chocolate candies is (600/25) = 24 times as many candies as 25 candies. Multiplying
 the number of candies by 24 multiplies the cost by 24, so 600 candies costs 24· 6 = 144
@@ -815,7 +812,7 @@
           <t>150</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="1" t="inlineStr">
         <is>
           <t>Let x be the number of paperclips that a box with a volume of 48 \textcm^3 could hold.
 Setting up the ratio (50/16)=(x/48) and solving for x gives x=150. Hence, a 48 \textcm^3
@@ -861,7 +858,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="1" t="inlineStr">
         <is>
           <t>Let there be B boys and G girls. Since every member is either a boy or a girl, B+G=26.
 Also, we have (1/2)G+B=16. Multiplying the second equation by 2, we get G+2B=32.
@@ -906,7 +903,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="1" t="inlineStr">
         <is>
           <t>Let there be B boys and G girls. Since every member is either a boy or a girl, B+G=26.
 Also, we have (1/2)G+B=16. Subtracting the second equation from the first, we have:
@@ -950,7 +947,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="1" t="inlineStr">
         <is>
           <t>To find the maximum height of the ball is to maximize the expression -16t^2+32t+15. We
 will do this by completing the square. Factoring a -16 from the first two terms, we have
@@ -998,7 +995,7 @@
           <t>95</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="1" t="inlineStr">
         <is>
           <t>To find the maximum height of the ball is to maximize the expression -16t^2+64t+31. We
 will do this by completing the square. Factoring a -16 from the first two terms, we have
@@ -1048,7 +1045,7 @@
           <t>\frac{25}{84}</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="1" t="inlineStr">
         <is>
           <t>Setting b = a and c = a, we get \[a \diamondsuit (a \diamondsuit a) = (a \diamondsuit a) ·
 a,\]which reduces to a \diamondsuit 1 = a for any nonzero a. Setting c = b, we get \[a
@@ -1096,7 +1093,7 @@
           <t>13</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="1" t="inlineStr">
         <is>
           <t>The store's revenue is given by: number of books sold × price of each book, or
 p(130-5p)=130p-5p^2. We want to maximize this expression by completing the square. We can
@@ -1146,7 +1143,7 @@
           <t>3025</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="1" t="inlineStr">
         <is>
           <t>The number of cards is 1 + 2 + 3 + \dots + n = (n(n + 1)/2), and the sum of the values of
 all cards is \[1^2 + 2^2 + 3^2 + \dots + n^2 = (n(n + 1)(2n + 1)/6).\]Therefore, the
@@ -1191,7 +1188,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="1" t="inlineStr">
         <is>
           <t>We see that the center of the ellipse is (2,-3), and that the major axis lies along the
 line x = 2. Since the ellipse is tangent to the x-axis, one end-point of the major axis
@@ -1242,7 +1239,7 @@
           <t>48</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="1" t="inlineStr">
         <is>
           <t>This is a geometric sequence with a first term of 3 and a common ratio of 2. At the end of
 the eighth day, we are at the 5th term of this sequence, so there are 3·2^4=48 cells then.</t>
@@ -1285,7 +1282,7 @@
           <t>\frac{1}{2}</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" s="1" t="inlineStr">
         <is>
           <t>Let one of the points of tangency be (a,a^2). By symmetry, other point of tangency is
 (-a,a^2). Also by symmetry, the center of the circle lies on the y-axis. Let the center be
@@ -1339,7 +1336,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="1" t="inlineStr">
         <is>
           <t>Let r be the radius of such a circle. Since the circle is tangent to the positive x-axis
 and positive y-axis, its center is (r,r). This circle is also tangent to the circle
@@ -1389,7 +1386,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" s="1" t="inlineStr">
         <is>
           <t>Let u=3x-1. Then x=(u+1)/3, and \beginalign* f(u)&amp;=((u+1/3))^2+(u+1/3)+1\\
 &amp;=(u^2+2u+1/9)+(u+1/3)+1\\ &amp;=(u^2+5u+13/9). \endalign*In particular, \[
@@ -1397,7 +1394,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="72" customHeight="1">
+    <row r="22" ht="144" customHeight="1">
       <c r="A22" s="1" t="n">
         <v>21</v>
       </c>
@@ -1423,20 +1420,24 @@
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>11. Find the greatest integer n such that the cubic polynomial n x3 −
-x2 + (n − 11)x − 400 6 has roots α2,β2, and γ2, where α,β, and γ are
-complex numbers, and there are exactly seven different possible values
-for α + β + γ.</t>
+          <t>Every morning Aya goes for a 9-kilometer-long walk and stops at a
+coffee shop afterwards. When she walks at a constant speed of s
+kilometers per hour, the walk takes her 4 hours, including t minutes
+spent in the coffee shop. When she walks s + 2 kilometers per hour,
+the walk takes her 2 hours and 24 minutes, including t minutes spent
+in the coffee shop. Suppose Aya walks at s + 1/2 kilometers per hour.
+Find the number of minutes the walk takes her, including the t minutes
+spent in the coffee shop.</t>
         </is>
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23" ht="54" customHeight="1">
+          <t>204</t>
+        </is>
+      </c>
+      <c r="H22" s="1" t="inlineStr"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
       <c r="A23" s="1" t="n">
         <v>22</v>
       </c>
@@ -1462,19 +1463,18 @@
       </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
-          <t>9. Let S denote the value of the infinite sum 1 1 1 1 + + + + ⋯ 9 99
-999 9999 Find the remainder when the greatest integer less than or
-equal to 10100S is divided by 1000.</t>
+          <t>There exist real numbers x and y, both greater than 1, such that
+log_x(y^x) = log_y(x^(4y)) = 10. Find xy.</t>
         </is>
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24" ht="54" customHeight="1">
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H23" s="1" t="inlineStr"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
       <c r="A24" s="1" t="n">
         <v>23</v>
       </c>
@@ -1500,19 +1500,18 @@
       </c>
       <c r="F24" s="1" t="inlineStr">
         <is>
-          <t>4. Find the number of ordered pairs (x,y), where both x and y are
-integers between −100 and 100, inclusive, such that 12x2 − xy − 6y2 =
-0.</t>
+          <t>Find the largest possible real part of (75 + 117i)z + (96 + 144i)/z,
+where z is a complex number with |z| = 4. Here i = sqrt(-1).</t>
         </is>
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25" ht="36" customHeight="1">
+          <t>540</t>
+        </is>
+      </c>
+      <c r="H24" s="1" t="inlineStr"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
       <c r="A25" s="1" t="n">
         <v>24</v>
       </c>
@@ -1538,16 +1537,17 @@
       </c>
       <c r="F25" s="1" t="inlineStr">
         <is>
-          <t>2. There exist real numbers x and y, both greater than 1, such that
-log (yx) = x log (x4y ) = 10. Find xy. y</t>
+          <t>Define f(x) = ||x| - 1/2| and g(x) = ||x| - 1/4|. Find the number of
+intersections of the graphs of y = 4g(f(sin(2*pi*x))) and x =
+4g(f(cos(3*pi*y))).</t>
         </is>
       </c>
       <c r="G25" s="1" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr"/>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="H25" s="1" t="inlineStr"/>
     </row>
     <row r="26" ht="72" customHeight="1">
       <c r="A26" s="1" t="n">
@@ -1575,20 +1575,20 @@
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
-          <t>4. The product 63 log (5k2−1) k ∏ log (5k2−4) k+1 k=4 log (515) 4 =
-log (512) 5 log (524) ⋅ 5 log (521) 6 log (535) ⋅ 6 log (532) 7 log
-(53968) 63 ⋯ log (53965) 64 is equal to m, where m and n are
-relatively prime positive integers. Find m + n. n</t>
+          <t>Let x, y, and z be positive real numbers that satisfy the following
+system of equations: log_2(x/(yz)) = 1/2, log_2(y/(xz)) = 1/3,
+log_2(z/(xy)) = 1/4. Then the value of |log_2(x^4 * y^3 * z^2)| is m/n
+where m and n are relatively prime positive integers. Find m + n.</t>
         </is>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27" ht="90" customHeight="1">
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H26" s="1" t="inlineStr"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
       <c r="A27" s="1" t="n">
         <v>26</v>
       </c>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>Hendrycks</t>
+          <t>AIME</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
@@ -1614,28 +1614,19 @@
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
-          <t>A ''super ball'' is dropped from a window 16 meters above the ground.
-On each bounce it rises \frac34 the distance of the preceding high
-point. The ball is caught when it reached the high point after hitting
-the ground for the third time. To the nearest meter, how far has it
-travelled?</t>
+          <t>Find the number of triples of nonnegative integers (a,b,c) satisfying
+a + b + c = 300 and a^2*b + a^2*c + b^2*a + b^2*c + c^2*a + c^2*b =
+6,000,000.</t>
         </is>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>The ball traveled 16+16·\frac34+16·(\frac34)^2 = 16+ 12+9 = 37 meters on its three
-descents. The ball also traveled 16·\frac34+16·(\frac34)^2+16·(\frac34)^3 = 12+9+\frac274
-= 27.75 meters on its three ascents. Thus, the ball traveled 37+27.75 = 64.75 \approx 65
-meters total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="90" customHeight="1">
+          <t>601</t>
+        </is>
+      </c>
+      <c r="H27" s="1" t="inlineStr"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
       <c r="A28" s="1" t="n">
         <v>27</v>
       </c>
@@ -1646,7 +1637,7 @@
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>Hendrycks</t>
+          <t>AIME</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
@@ -1661,28 +1652,19 @@
       </c>
       <c r="F28" s="1" t="inlineStr">
         <is>
-          <t>A car travels the 120 miles from A to B at 60 miles per hour, and then
-returns to A on the same road. If the average rate of the round trip
-is 45 miles per hour, what is the rate, in miles per hour, of the car
-traveling back from B to A?</t>
+          <t>Find the number of ordered pairs (x,y), where both x and y are
+integers between -100 and 100, inclusive, such that 12x^2 - xy - 6y^2
+= 0.</t>
         </is>
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Let d denote the number of miles in the distance from A to B and let r denote the speed of
-the car (in miles per hour) on the return trip. It takes d/60 hours to travel from A to B
-and d/r hours to travel from B to A. Round trip, 2d miles are covered in d/60+d/r hours
-for an average speed of \[ (2d/\fracd)60+(d/r) · (\frac60/d)(60/d) = (120/1+\frac60)r \]
-Setting this expression equal to 45, we find r=36.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="270" customHeight="1">
+          <t>117</t>
+        </is>
+      </c>
+      <c r="H28" s="1" t="inlineStr"/>
+    </row>
+    <row r="29" ht="90" customHeight="1">
       <c r="A29" s="1" t="n">
         <v>28</v>
       </c>
@@ -1693,7 +1675,7 @@
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>Hendrycks</t>
+          <t>AIME</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
@@ -1708,37 +1690,21 @@
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
-          <t>A lattice point is a point whose coordinates are both integers. How
-many lattice points are on the boundary or inside the region bounded
-by y=|x| and y=-x^2+6?</t>
+          <t>The product, for k = 4 to 63, of [log_k(5^(k^2-1)) /
+log_(k+1)(5^(k^2-4))] = [log_4(5^15)/log_5(5^12)] *
+[log_5(5^24)/log_6(5^21)] * [log_6(5^35)/log_7(5^32)] * ... *
+[log_63(5^3968)/log_64(5^3965)] is equal to m/n, where m and n are
+relatively prime positive integers. Find m + n.</t>
         </is>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>The graph of the two equations is shown below: [asy] Label f; f.p=fontsize(4);
-xaxis(-3,3,Ticks(f, 2.0)); yaxis(-1,7,Ticks(f, 2.0)); real f(real x) return abs(x);
-draw(graph(f,-3,3), linewidth(1)); real g(real x) return -x^2+6; draw(graph(g,-2.5,2.5),
-linewidth(1)); [/asy] We first find the x values at which the two equations intersect.
-When x≥ 0, y=|x|=x. Plugging this into the second equation to eliminate y, we get
-x=-x^2+6\Rightarrow x^2+x-6=0. Factoring the left hand side gives (x+3)(x-2)=0, so x=2
-(since we stated the x was non-negative). By symmetry, the x value of the left
-intersection is x=-2. So we just have to consider the integer x values between these two
-bounds and find all integer y values that make the point (x,y) fall inside the region. For
-x=-2, there is 1 point that works: (-2,2). For x=-1, the value of y=|x| is y=1 and the
-value of y=-x^2+6 is y=5, so all y values between 1 and 5 inclusive work, for a total of 5
-points. For x=0, the value of y=|x| is y=0 and the value of y=-x^2+6 is y=6, so all y
-values between 0 and 6 inclusive work, for a total of 7 points. By symmetry, when x=1,
-there are 5 points that work, and when x=2, there is 1 point that works. In total, there
-are 1+5+7+5+1=19 lattice points in the region or on the boundary.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="72" customHeight="1">
+          <t>106</t>
+        </is>
+      </c>
+      <c r="H29" s="1" t="inlineStr"/>
+    </row>
+    <row r="30" ht="54" customHeight="1">
       <c r="A30" s="1" t="n">
         <v>29</v>
       </c>
@@ -1749,7 +1715,7 @@
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>Hendrycks</t>
+          <t>AIME</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
@@ -1764,25 +1730,19 @@
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
-          <t>How many four-digit numbers N have the property that the three-digit
-number obtained by removing the leftmost digit is one ninth of N?</t>
+          <t>There are n values of x in the interval 0 &lt; x &lt; 2*pi where f(x) =
+sin(7*pi * sin(5x)) = 0. For t of these n values of x, the graph of y
+= f(x) is tangent to the x-axis. Find n + t.</t>
         </is>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Let a denote the leftmost digit of N and let x denote the three-digit number obtained by
-removing a. Then N=1000a+x=9x and it follows that 1000a=8x. Dividing both sides by 8
-yields 125a=x. All the values of a in the range 1 to 7 result in three-digit numbers,
-hence there are 7 values for N.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="162" customHeight="1">
+          <t>149</t>
+        </is>
+      </c>
+      <c r="H30" s="1" t="inlineStr"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
       <c r="A31" s="1" t="n">
         <v>30</v>
       </c>
@@ -1793,7 +1753,7 @@
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>Hendrycks</t>
+          <t>AIME</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
@@ -1808,63 +1768,290 @@
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>How many integers are solutions to the equation (x-2)^(25-x^2)=1?</t>
+          <t>Let the sequence of rationals x_1, x_2, ... be defined such that x_1 =
+25/11 and x_(k+1) = (1/3) * (x_k + 1/x_k - 1) for all k ≥ 1. Then
+x_2025 can be expressed as m/n for relatively prime positive integers
+m and n. Find the remainder when m + n is divided by 1000.</t>
         </is>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>We need some basic facts from number theory: a^0 = 1 for any a, 1^b = 1 for any b, and
-(-1)^c = 1 if c is an even integer. Unless the base is a complex number (which is excluded
-since we are looking for integer solutions), there are no other ways to get an RHS of 1.
-Thus, either the exponent is zero (giving the equation 25 - x^2 = 0), the base is 1
-(giving x -2 = 1), or the base is -1 and the exponent is even (giving the simultaneous
-equations x - 2 = -1 and 25 - x^2 = 2n for some integer n). Solving the first equation
-gives x = \pm 5, and solving the second gives x = 3. The third equation implies that x =
-1, in which case 25 - x^2 = 24 is indeed even, so x = 1 is a valid solution. In all, there
-are 4 integer solutions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="108" customHeight="1">
+          <t>248</t>
+        </is>
+      </c>
+      <c r="H31" s="1" t="inlineStr"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
       <c r="A32" s="1" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
+          <t>ALG_H_011</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>Algebra</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>There are exactly three positive real numbers k such that the function
+f(x) = (x-18)(x-72)(x-98)(x-k)/x, defined over the positive real
+numbers, achieves its minimum value at exactly two positive real
+numbers x. Find the sum of these three values of k.</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="H32" s="1" t="inlineStr"/>
+    </row>
+    <row r="33" ht="180" customHeight="1">
+      <c r="A33" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>ALG_H_012</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="inlineStr">
+        <is>
+          <t>Algebra</t>
+        </is>
+      </c>
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F33" s="1" t="inlineStr">
+        <is>
+          <t>Patrick started walking at a constant speed along a straight road from
+his school to the park. One hour after Patrick left, Tanya started
+running at a constant speed of 2 miles per hour faster than Patrick
+walked, following the same straight road from the school to the park.
+One hour after Tanya left, Jose started bicycling at a constant speed
+of 7 miles per hour faster than Tanya ran, following the same straight
+road from the school to the park. All three people arrived at the park
+at the same time. The distance from the school to the park is m/n
+miles, where m and n are relatively prime positive integers. Find m +
+n.</t>
+        </is>
+      </c>
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="H33" s="1" t="inlineStr"/>
+    </row>
+    <row r="34" ht="54" customHeight="1">
+      <c r="A34" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>ALG_H_013</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="inlineStr">
+        <is>
+          <t>Algebra</t>
+        </is>
+      </c>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t>The product of all positive real numbers x satisfying the equation
+the-20th-root-of(x^(log_2026 x)) = 26x is an integer P. Find the
+number of positive integer divisors of P.</t>
+        </is>
+      </c>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="H34" s="1" t="inlineStr"/>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>ALG_H_014</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="inlineStr">
+        <is>
+          <t>Algebra</t>
+        </is>
+      </c>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F35" s="1" t="inlineStr">
+        <is>
+          <t>Find the sum of the 10th terms of all arithmetic sequences of integers
+that have first term equal to 4 and include both 24 and 34 as terms.</t>
+        </is>
+      </c>
+      <c r="G35" s="1" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="H35" s="1" t="inlineStr"/>
+    </row>
+    <row r="36" ht="54" customHeight="1">
+      <c r="A36" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>ALG_H_015</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="inlineStr">
+        <is>
+          <t>Algebra</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F36" s="1" t="inlineStr">
+        <is>
+          <t>Let S denote the value of the infinite sum 1/9 + 1/99 + 1/999 + 1/9999
++ .... Find the remainder when the greatest integer less than or equal
+to 10^100 * S is divided by 1000.</t>
+        </is>
+      </c>
+      <c r="G36" s="1" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="H36" s="1" t="inlineStr"/>
+    </row>
+    <row r="37" ht="72" customHeight="1">
+      <c r="A37" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>ALG_H_016</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="inlineStr">
+        <is>
+          <t>Algebra</t>
+        </is>
+      </c>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F37" s="1" t="inlineStr">
+        <is>
+          <t>Find the greatest integer n such that the cubic polynomial x^3 -
+(n/6)*x^2 + (n-11)*x - 400 has roots alpha^2, beta^2, and gamma^2,
+where alpha, beta, and gamma are complex numbers, and there are
+exactly seven different possible values for alpha + beta + gamma.</t>
+        </is>
+      </c>
+      <c r="G37" s="1" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="H37" s="1" t="inlineStr"/>
+    </row>
+    <row r="38" ht="108" customHeight="1">
+      <c r="A38" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
           <t>NT_E_001</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E32" s="1" t="inlineStr">
+      <c r="E38" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F32" s="1" t="inlineStr">
+      <c r="F38" s="1" t="inlineStr">
         <is>
           <t>100_10 in base b has exactly 5 digits. What is the value of b?</t>
         </is>
       </c>
-      <c r="G32" s="1" t="inlineStr">
+      <c r="G38" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H38" s="1" t="inlineStr">
         <is>
           <t>For a base b representation of 100_10 to have exactly 5 digits, the largest power of b
 that is less than 100 must be 4. Therefore, we have the requirement that b^4 ≤ 100 &lt; b^5.
@@ -1875,31 +2062,31 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="72" customHeight="1">
-      <c r="A33" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="1" t="inlineStr">
+    <row r="39" ht="72" customHeight="1">
+      <c r="A39" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
         <is>
           <t>NT_E_002</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E33" s="1" t="inlineStr">
+      <c r="E39" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F33" s="1" t="inlineStr">
+      <c r="F39" s="1" t="inlineStr">
         <is>
           <t>A Mersenne prime is defined to be a prime number of the form 2^n - 1,
 where n must itself be a prime. For example, since 2^3 - 1 = 7, and 3
@@ -1907,43 +2094,43 @@
 prime less than 200?</t>
         </is>
       </c>
-      <c r="G33" s="1" t="inlineStr">
+      <c r="G39" s="1" t="inlineStr">
         <is>
           <t>127</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H39" s="1" t="inlineStr">
         <is>
           <t>The largest Mersenne Prime less than 200 is 2^7 - 1 = 128 - 1 = 127. The next possible
 Mersenne Prime, 2^11 - 1 = 2047, is much too large (and is not prime).</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="72" customHeight="1">
-      <c r="A34" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="1" t="inlineStr">
+    <row r="40" ht="72" customHeight="1">
+      <c r="A40" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
         <is>
           <t>NT_E_003</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E34" s="1" t="inlineStr">
+      <c r="E40" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F34" s="1" t="inlineStr">
+      <c r="F40" s="1" t="inlineStr">
         <is>
           <t>A bag of grapes is to be distributed evenly to 5 kids in a class, and
 the grapes that are left over will be thrown out. If each student
@@ -1951,12 +2138,12 @@
 possible number of grapes that could be thrown out?</t>
         </is>
       </c>
-      <c r="G34" s="1" t="inlineStr">
+      <c r="G40" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H40" s="1" t="inlineStr">
         <is>
           <t>If we have at least 5 grapes left, we can give each student one more, so they do not have
 the greatest possible number. On the other hand, if we have 4 grapes left, we cannot give
@@ -1965,31 +2152,31 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="72" customHeight="1">
-      <c r="A35" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="1" t="inlineStr">
+    <row r="41" ht="72" customHeight="1">
+      <c r="A41" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
         <is>
           <t>NT_E_004</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E35" s="1" t="inlineStr">
+      <c r="E41" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F35" s="1" t="inlineStr">
+      <c r="F41" s="1" t="inlineStr">
         <is>
           <t>A marathon is 26 miles and 385 yards. One mile equals 1760 yards.
 Leila has run ten marathons in her life. If the total distance Leila
@@ -1997,12 +2184,12 @@
 what is the value of y?</t>
         </is>
       </c>
-      <c r="G35" s="1" t="inlineStr">
+      <c r="G41" s="1" t="inlineStr">
         <is>
           <t>330</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H41" s="1" t="inlineStr">
         <is>
           <t>If one marathon equals 26 miles and 385 yards, then ten marathons equal 260 miles and 3850
 yards. Those 3850 yards can be broken down as 2 miles and 3850 - (2· 1760) = 3850 - 3520 =
@@ -2010,31 +2197,31 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="126" customHeight="1">
-      <c r="A36" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="1" t="inlineStr">
+    <row r="42" ht="126" customHeight="1">
+      <c r="A42" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
         <is>
           <t>NT_E_005</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E36" s="1" t="inlineStr">
+      <c r="E42" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F36" s="1" t="inlineStr">
+      <c r="F42" s="1" t="inlineStr">
         <is>
           <t>A math class has fewer than 40 students. When the students try to sit
 in rows of 7, 3 students sit in the last row. When the students try to
@@ -2042,12 +2229,12 @@
 are in this class?</t>
         </is>
       </c>
-      <c r="G36" s="1" t="inlineStr">
+      <c r="G42" s="1" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H42" s="1" t="inlineStr">
         <is>
           <t>Let n be the number of students in the class. When we divide n by 7, we get a remainder of
 3. Therefore, we need to add multiples of 7 to 3 until we get a number which, when we
@@ -2059,31 +2246,31 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="108" customHeight="1">
-      <c r="A37" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="1" t="inlineStr">
+    <row r="43" ht="108" customHeight="1">
+      <c r="A43" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
         <is>
           <t>NT_E_006</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E37" s="1" t="inlineStr">
+      <c r="E43" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F37" s="1" t="inlineStr">
+      <c r="F43" s="1" t="inlineStr">
         <is>
           <t>A number is divisible by 8 if the number formed by its last 3 digits
 is divisible by 8. For example, the number 47389248 is divisible by 8
@@ -2093,12 +2280,12 @@
 of A?</t>
         </is>
       </c>
-      <c r="G37" s="1" t="inlineStr">
+      <c r="G43" s="1" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H43" s="1" t="inlineStr">
         <is>
           <t>For 9924661A6 to be divisible by 8, we must have 1A6 divisible by 8. We check each of the
 possibilities, using a calculator or by checking by hand: \bullet 106 is not divisible by
@@ -2109,41 +2296,41 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="72" customHeight="1">
-      <c r="A38" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="1" t="inlineStr">
+    <row r="44" ht="72" customHeight="1">
+      <c r="A44" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
         <is>
           <t>NT_E_007</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E38" s="1" t="inlineStr">
+      <c r="E44" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F38" s="1" t="inlineStr">
+      <c r="F44" s="1" t="inlineStr">
         <is>
           <t>A number n has 3 divisors. How many divisors does n^2 have?</t>
         </is>
       </c>
-      <c r="G38" s="1" t="inlineStr">
+      <c r="G44" s="1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H44" s="1" t="inlineStr">
         <is>
           <t>If n has 3 divisors, since it is divisible by both 1 and n, the only possibility for a
 third unique divisor is √n, which must be prime. Therefore, n is the square of a prime
@@ -2152,43 +2339,43 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="54" customHeight="1">
-      <c r="A39" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="1" t="inlineStr">
+    <row r="45" ht="54" customHeight="1">
+      <c r="A45" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
         <is>
           <t>NT_E_008</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E39" s="1" t="inlineStr">
+      <c r="E45" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F39" s="1" t="inlineStr">
+      <c r="F45" s="1" t="inlineStr">
         <is>
           <t>A positive two-digit number is even and is a multiple of 11. The
 product of its digits is a perfect cube. What is this two-digit
 number?</t>
         </is>
       </c>
-      <c r="G39" s="1" t="inlineStr">
+      <c r="G45" s="1" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H45" s="1" t="inlineStr">
         <is>
           <t>Let N be the desired two-digit number. N is divisible by 2 and by 11, and (2,11)=1, so N
 is divisible by 22. Thus, N\in\22, 44, 66, 88\. Only 88 is such that the product of its
@@ -2196,31 +2383,31 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="90" customHeight="1">
-      <c r="A40" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="1" t="inlineStr">
+    <row r="46" ht="90" customHeight="1">
+      <c r="A46" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
         <is>
           <t>NT_E_009</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E40" s="1" t="inlineStr">
+      <c r="E46" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F40" s="1" t="inlineStr">
+      <c r="F46" s="1" t="inlineStr">
         <is>
           <t>A total of 180 marbles (gray, white, and black) are placed in a line.
 The first five are gray, followed by four white, followed by three
@@ -2229,12 +2416,12 @@
 158th marble in this line?</t>
         </is>
       </c>
-      <c r="G40" s="1" t="inlineStr">
+      <c r="G46" s="1" t="inlineStr">
         <is>
           <t>\text{gray}</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H46" s="1" t="inlineStr">
         <is>
           <t>We notice that the marbles appear in strings of 5 gray, 4 white, 3 black. These strings
 have 12 marbles each. Since \[158=13·12+2,\]there are 13 full strings of marbles and 2
@@ -2243,43 +2430,43 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="72" customHeight="1">
-      <c r="A41" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="1" t="inlineStr">
+    <row r="47" ht="72" customHeight="1">
+      <c r="A47" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="1" t="inlineStr">
         <is>
           <t>NT_E_010</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E41" s="1" t="inlineStr">
+      <c r="E47" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F41" s="1" t="inlineStr">
+      <c r="F47" s="1" t="inlineStr">
         <is>
           <t>A whole number is said to be ''9-heavy'' if the remainder when the
 number is divided by 9 is greater than 5. What is the least three-
 digit 9-heavy whole number?</t>
         </is>
       </c>
-      <c r="G41" s="1" t="inlineStr">
+      <c r="G47" s="1" t="inlineStr">
         <is>
           <t>105</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H47" s="1" t="inlineStr">
         <is>
           <t>We begin by computing the residue of the smallest three digit number modulo 9. We have
 \[100\equiv1\pmod9.\] Therefore 100 is not 9-heavy. Counting up from 100 we notice that
@@ -2288,31 +2475,31 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="72" customHeight="1">
-      <c r="A42" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="1" t="inlineStr">
+    <row r="48" ht="72" customHeight="1">
+      <c r="A48" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
         <is>
           <t>NT_M_001</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E42" s="1" t="inlineStr">
+      <c r="E48" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F42" s="1" t="inlineStr">
+      <c r="F48" s="1" t="inlineStr">
         <is>
           <t>A \textitcomposite number is a number that has two or more prime
 factors. The number 87 can be expressed as the sum of two composite
@@ -2320,12 +2507,12 @@
 two such numbers?</t>
         </is>
       </c>
-      <c r="G42" s="1" t="inlineStr">
+      <c r="G48" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H48" s="1" t="inlineStr">
         <is>
           <t>The minimum difference between two numbers whose sum is 87 is achieved when the numbers
 are as close as possible to 87\div2=43.5. These numbers are 43 and 44, but 43 is prime, so
@@ -2334,43 +2521,43 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="72" customHeight="1">
-      <c r="A43" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="1" t="inlineStr">
+    <row r="49" ht="72" customHeight="1">
+      <c r="A49" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
         <is>
           <t>NT_M_002</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E43" s="1" t="inlineStr">
+      <c r="E49" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F43" s="1" t="inlineStr">
+      <c r="F49" s="1" t="inlineStr">
         <is>
           <t>A \textitpalindrome is a number which reads the same forward as
 backward. For example, 343 and 1221 are palindromes. What is the least
 natural number that can be added to 40,305 to create a palindrome?</t>
         </is>
       </c>
-      <c r="G43" s="1" t="inlineStr">
+      <c r="G49" s="1" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H49" s="1" t="inlineStr">
         <is>
           <t>We are asked to find the positive difference between 40305 and the least palindrome
 greater than 40305. The only five-digit palindrome beginning with 403 is 40304, which is
@@ -2379,31 +2566,31 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="72" customHeight="1">
-      <c r="A44" s="1" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="1" t="inlineStr">
+    <row r="50" ht="72" customHeight="1">
+      <c r="A50" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="1" t="inlineStr">
         <is>
           <t>NT_M_003</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E44" s="1" t="inlineStr">
+      <c r="E50" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F44" s="1" t="inlineStr">
+      <c r="F50" s="1" t="inlineStr">
         <is>
           <t>A band has 72 members who will all be marching during halftime. They
 need to march in rows with the same number of students per row. If
@@ -2411,12 +2598,12 @@
 row-lengths can the band be arranged?</t>
         </is>
       </c>
-      <c r="G44" s="1" t="inlineStr">
+      <c r="G50" s="1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H50" s="1" t="inlineStr">
         <is>
           <t>If x members march in each row and there is a total of y rows, then xy=72=2^3·3^2. Given
 that 5≤ x≤20, the possible values for x are 2^3=8, 2^2·3=12, 2·3=6, 2·3^2=18 and 3^2=9,
@@ -2424,31 +2611,31 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="126" customHeight="1">
-      <c r="A45" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="1" t="inlineStr">
+    <row r="51" ht="126" customHeight="1">
+      <c r="A51" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1" t="inlineStr">
         <is>
           <t>NT_M_004</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E45" s="1" t="inlineStr">
+      <c r="E51" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F45" s="1" t="inlineStr">
+      <c r="F51" s="1" t="inlineStr">
         <is>
           <t>A box contains gold coins. If the coins are equally divided among six
 people, four coins are left over. If the coins are equally divided
@@ -2457,12 +2644,12 @@
 coins are left when equally divided among seven people?</t>
         </is>
       </c>
-      <c r="G45" s="1" t="inlineStr">
+      <c r="G51" s="1" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H51" s="1" t="inlineStr">
         <is>
           <t>The counting numbers that leave a remainder of 4 when divided by 6 are \[4, 10, 16, 22,
 28, 34, \ldots.\] The counting numbers that leave a remainder of 3 when divided by 5 are
@@ -2474,31 +2661,31 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="108" customHeight="1">
-      <c r="A46" s="1" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="1" t="inlineStr">
+    <row r="52" ht="108" customHeight="1">
+      <c r="A52" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1" t="inlineStr">
         <is>
           <t>NT_M_005</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E46" s="1" t="inlineStr">
+      <c r="E52" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F46" s="1" t="inlineStr">
+      <c r="F52" s="1" t="inlineStr">
         <is>
           <t>A box contains tiles, numbered 1, 2, 3,..., 49, 50. Only tiles which
 are marked with a number congruent to 2 \pmod5 are blue. One tile is
@@ -2506,12 +2693,12 @@
 blue?</t>
         </is>
       </c>
-      <c r="G46" s="1" t="inlineStr">
+      <c r="G52" s="1" t="inlineStr">
         <is>
           <t>\frac{1}{5}</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H52" s="1" t="inlineStr">
         <is>
           <t>Positive integers which are congruent to 2\pmod5 belong to the set \2+5(0), 2+5(1),
 2+5(2), ..., \.To find the largest element of this set which is less than or equal to 50,
@@ -2522,72 +2709,72 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="36" customHeight="1">
-      <c r="A47" s="1" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="1" t="inlineStr">
+    <row r="53" ht="36" customHeight="1">
+      <c r="A53" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="1" t="inlineStr">
         <is>
           <t>NT_M_006</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="inlineStr">
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E47" s="1" t="inlineStr">
+      <c r="E53" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F47" s="1" t="inlineStr">
+      <c r="F53" s="1" t="inlineStr">
         <is>
           <t>A cat has found 432_9 methods in which to extend each of her nine
 lives. How many methods are there in base 10?</t>
         </is>
       </c>
-      <c r="G47" s="1" t="inlineStr">
+      <c r="G53" s="1" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H53" s="1" t="inlineStr">
         <is>
           <t>432_9 = 2·9^0+3·9^1+4·9^2 = 2+27+324 = 353.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="72" customHeight="1">
-      <c r="A48" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="1" t="inlineStr">
+    <row r="54" ht="72" customHeight="1">
+      <c r="A54" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="1" t="inlineStr">
         <is>
           <t>NT_M_007</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E48" s="1" t="inlineStr">
+      <c r="E54" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F48" s="1" t="inlineStr">
+      <c r="F54" s="1" t="inlineStr">
         <is>
           <t>A day can be evenly divided into 86,400 periods of 1 second; 43,200
 periods of each 2 seconds; or in many other ways. In total, how many
@@ -2595,12 +2782,12 @@
 and m are positive integers?</t>
         </is>
       </c>
-      <c r="G48" s="1" t="inlineStr">
+      <c r="G54" s="1" t="inlineStr">
         <is>
           <t>96</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H54" s="1" t="inlineStr">
         <is>
           <t>A day has 86,400 seconds. 86,400=2^7·3^3·5^2, so 86,400 has (7+1)(3+1)(2+1)=96 positive
 factors. Thus there are 96/2=48 (unordered) pairs of factors each of whose product is
@@ -2609,42 +2796,42 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="90" customHeight="1">
-      <c r="A49" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="1" t="inlineStr">
+    <row r="55" ht="90" customHeight="1">
+      <c r="A55" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1" t="inlineStr">
         <is>
           <t>NT_M_008</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D49" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D55" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E49" s="1" t="inlineStr">
+      <c r="E55" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F49" s="1" t="inlineStr">
+      <c r="F55" s="1" t="inlineStr">
         <is>
           <t>A divisor of a number is a proper divisor if it is not equal to the
 number. What is the sum of the proper divisors of 432?</t>
         </is>
       </c>
-      <c r="G49" s="1" t="inlineStr">
+      <c r="G55" s="1" t="inlineStr">
         <is>
           <t>808</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H55" s="1" t="inlineStr">
         <is>
           <t>The prime factorization of 432 = 2^4 · 3^3. It follows that the sum of the divisors is
 equal to (1 + 2 + 2^2 + 2^3 + 2^4)(1 + 3 + 3^2 + 3^3), as each factor of 432 is
@@ -2654,31 +2841,31 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="162" customHeight="1">
-      <c r="A50" s="1" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="1" t="inlineStr">
+    <row r="56" ht="162" customHeight="1">
+      <c r="A56" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
         <is>
           <t>NT_M_009</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E50" s="1" t="inlineStr">
+      <c r="E56" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F50" s="1" t="inlineStr">
+      <c r="F56" s="1" t="inlineStr">
         <is>
           <t>A magic square is an array of numbers in which the sum of the numbers
 in each row, in each column, and along the two main diagonals are
@@ -2691,12 +2878,12 @@
 label("13",(0.5,2),N); label("14",(1.5,0),N); [/asy]</t>
         </is>
       </c>
-      <c r="G50" s="1" t="inlineStr">
+      <c r="G56" s="1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H56" s="1" t="inlineStr">
         <is>
           <t>Let b be the base in which the numbers in the square are expressed. The first row and the
 first column must have the same sum, which implies that 1+11_b = 4+3. Writing 11_b as b+1,
@@ -2704,42 +2891,42 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="90" customHeight="1">
-      <c r="A51" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="1" t="inlineStr">
+    <row r="57" ht="90" customHeight="1">
+      <c r="A57" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="1" t="inlineStr">
         <is>
           <t>NT_M_010</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E51" s="1" t="inlineStr">
+      <c r="E57" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F51" s="1" t="inlineStr">
+      <c r="F57" s="1" t="inlineStr">
         <is>
           <t>A natural number is abundant if it is less than the sum of its proper
 divisors. What is the smallest abundant number?</t>
         </is>
       </c>
-      <c r="G51" s="1" t="inlineStr">
+      <c r="G57" s="1" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H57" s="1" t="inlineStr">
         <is>
           <t>For any prime number, the sum of its proper divisors is equal to 1, so a prime number
 cannot be an abundant number. Therefore, it suffices to check only composite numbers:
@@ -2749,469 +2936,452 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="72" customHeight="1">
-      <c r="A52" s="1" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" s="1" t="inlineStr">
+    <row r="58" ht="54" customHeight="1">
+      <c r="A58" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="1" t="inlineStr">
         <is>
           <t>NT_H_001</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>AIME</t>
         </is>
       </c>
-      <c r="D52" s="1" t="inlineStr">
+      <c r="D58" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E52" s="1" t="inlineStr">
+      <c r="E58" s="1" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F52" s="1" t="inlineStr">
-        <is>
-          <t>7. Let N be the greatest four-digit integer with the property that
+      <c r="F58" s="1" t="inlineStr">
+        <is>
+          <t>Let p be the least prime number for which there exists an integer n
+such that n^4 + 1 is divisible by p^2. Find the least positive integer
+m such that m^4 + 1 is divisible by p^2.</t>
+        </is>
+      </c>
+      <c r="G58" s="1" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="H58" s="1" t="inlineStr"/>
+    </row>
+    <row r="59" ht="72" customHeight="1">
+      <c r="A59" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="1" t="inlineStr">
+        <is>
+          <t>NT_H_002</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D59" s="1" t="inlineStr">
+        <is>
+          <t>Number Theory</t>
+        </is>
+      </c>
+      <c r="E59" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F59" s="1" t="inlineStr">
+        <is>
+          <t>Let N be the greatest four-digit integer with the property that
 whenever one of its digits is changed to 1, the resulting number is
 divisible by 7. Let Q and R be the quotient and remainder,
 respectively, when N is divided by 1000. Find Q + R.</t>
         </is>
       </c>
-      <c r="G52" s="1" t="inlineStr">
+      <c r="G59" s="1" t="inlineStr">
         <is>
           <t>699</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53" ht="54" customHeight="1">
-      <c r="A53" s="1" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>NT_H_002</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="H59" s="1" t="inlineStr"/>
+    </row>
+    <row r="60" ht="54" customHeight="1">
+      <c r="A60" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="1" t="inlineStr">
+        <is>
+          <t>NT_H_003</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>AIME</t>
         </is>
       </c>
-      <c r="D53" s="1" t="inlineStr">
+      <c r="D60" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E53" s="1" t="inlineStr">
+      <c r="E60" s="1" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F53" s="1" t="inlineStr">
-        <is>
-          <t>8. Let N be the number of positive integer divisors of 1701717 that
-leave a remainder of 5 upon division by 12. Find the remainder when N
-is divided by 1000.</t>
-        </is>
-      </c>
-      <c r="G53" s="1" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54" ht="54" customHeight="1">
-      <c r="A54" s="1" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>NT_H_003</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="F60" s="1" t="inlineStr">
+        <is>
+          <t>Let omega ≠ 1 be a 13th root of unity. Find the remainder when the
+product, for k = 0 to 12, of (2 - 2*omega^k + omega^(2k)) is divided
+by 1000.</t>
+        </is>
+      </c>
+      <c r="G60" s="1" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="H60" s="1" t="inlineStr"/>
+    </row>
+    <row r="61" ht="90" customHeight="1">
+      <c r="A61" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="1" t="inlineStr">
+        <is>
+          <t>NT_H_004</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>AIME</t>
         </is>
       </c>
-      <c r="D54" s="1" t="inlineStr">
+      <c r="D61" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E54" s="1" t="inlineStr">
+      <c r="E61" s="1" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F54" s="1" t="inlineStr">
-        <is>
-          <t>13. Let p be the least prime number for which there exists an integer
-n such that n4 + 1 is divisible by p2. Find the least positive integer
-m such that m4 + 1 is divisible by p2.</t>
-        </is>
-      </c>
-      <c r="G54" s="1" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55" ht="54" customHeight="1">
-      <c r="A55" s="1" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" s="1" t="inlineStr">
-        <is>
-          <t>NT_H_004</t>
-        </is>
-      </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="F61" s="1" t="inlineStr">
+        <is>
+          <t>Let b ≥ 2 be an integer. Call a positive integer n b-eautiful if it
+has exactly two digits when expressed in base b and these two digits
+sum to sqrt(n). For example, 81 is 13-eautiful because 81 = 63 in base
+13 and 6 + 3 = sqrt(81). Find the least integer b ≥ 2 for which there
+are more than ten b-eautiful integers.</t>
+        </is>
+      </c>
+      <c r="G61" s="1" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="H61" s="1" t="inlineStr"/>
+    </row>
+    <row r="62" ht="36" customHeight="1">
+      <c r="A62" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="1" t="inlineStr">
+        <is>
+          <t>NT_H_005</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>AIME</t>
         </is>
       </c>
-      <c r="D55" s="1" t="inlineStr">
+      <c r="D62" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E55" s="1" t="inlineStr">
+      <c r="E62" s="1" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F55" s="1" t="inlineStr">
-        <is>
-          <t>15. Let N denote the number of ordered triples of positive integers
-(a,b,c) such that a,b,c ≤ 36 and a3 + b3 + c3 is a multiple of 37.
-Find the remainder when N is divided by 1000.</t>
-        </is>
-      </c>
-      <c r="G55" s="1" t="inlineStr">
-        <is>
-          <t>735</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56" ht="72" customHeight="1">
-      <c r="A56" s="1" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>NT_H_005</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="F62" s="1" t="inlineStr">
+        <is>
+          <t>Find the sum of all integer bases b &gt; 9 for which 17 (in base b) is a
+divisor of 97 (in base b).</t>
+        </is>
+      </c>
+      <c r="G62" s="1" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H62" s="1" t="inlineStr"/>
+    </row>
+    <row r="63" ht="72" customHeight="1">
+      <c r="A63" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="1" t="inlineStr">
+        <is>
+          <t>NT_H_006</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>AIME</t>
         </is>
       </c>
-      <c r="D56" s="1" t="inlineStr">
+      <c r="D63" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E56" s="1" t="inlineStr">
+      <c r="E63" s="1" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F56" s="1" t="inlineStr">
-        <is>
-          <t>5. There are 8! = 40320 eight-digit positive integers that use each of
+      <c r="F63" s="1" t="inlineStr">
+        <is>
+          <t>There are 8! = 40320 eight-digit positive integers that use each of
 the digits 1,2,3,4,5,6,7,8 exactly once. Let N be the number of these
 integers that are divisible by 22. Find the difference between N and
 2025.</t>
         </is>
       </c>
-      <c r="G56" s="1" t="inlineStr">
+      <c r="G63" s="1" t="inlineStr">
         <is>
           <t>279</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57" ht="144" customHeight="1">
-      <c r="A57" s="1" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>NT_H_006</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
+      <c r="H63" s="1" t="inlineStr"/>
+    </row>
+    <row r="64" ht="54" customHeight="1">
+      <c r="A64" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="1" t="inlineStr">
+        <is>
+          <t>NT_H_007</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D64" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E57" s="1" t="inlineStr">
+      <c r="E64" s="1" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F57" s="1" t="inlineStr">
-        <is>
-          <t>"Modulo m graph paper" consists of a grid of m^2 points, representing
-all pairs of integer residues (x,y) where 0≤ x, y &lt;m. To graph a
-congruence on modulo m graph paper, we mark every point (x,y) that
-satisfies the congruence. For example, a graph of y\equiv x^2\pmod 5
-would consist of the points (0,0), (1,1), (2,4), (3,4), and (4,1). The
-graph of 3x\equiv 4y-1 \pmod35has a single x-intercept (x_0,0) and a
-single y-intercept (0,y_0), where 0≤ x_0,y_0&lt;35. What is the value of
-x_0+y_0?</t>
-        </is>
-      </c>
-      <c r="G57" s="1" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>To find the x-intercept, we plug in 0 for y and solve 3x\equiv 4(0)-1 \pmod35.Multiplying
-both sides by 12, we get 36x \equiv -12\pmod35and thus x\equiv -12\pmod35. Translating
-this to the interval 0≤ x&lt;35, we have x\equiv 23\pmod35, so the x-intercept on our graph
-is at (23,0). To find the y-intercept, we plug in 0 for x and solve 3(0)\equiv 4y-1
-\pmod35.We can rewrite this as 1\equiv 4y\pmod35.Multiplying both sides by 9, we get
-9\equiv 36y\pmod35,and thus y\equiv 9\pmod35. So the y-intercept is at (0,9). We have
-x_0+y_0 = 23+9 = 32.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="144" customHeight="1">
-      <c r="A58" s="1" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>NT_H_007</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="inlineStr">
+      <c r="F64" s="1" t="inlineStr">
+        <is>
+          <t>Let N denote the number of ordered triples of positive integers
+(a,b,c) such that a,b,c ≤ 3^6 and a^3 + b^3 + c^3 is a multiple of
+3^7. Find the remainder when N is divided by 1000.</t>
+        </is>
+      </c>
+      <c r="G64" s="1" t="inlineStr">
+        <is>
+          <t>735</t>
+        </is>
+      </c>
+      <c r="H64" s="1" t="inlineStr"/>
+    </row>
+    <row r="65" ht="36" customHeight="1">
+      <c r="A65" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="1" t="inlineStr">
+        <is>
+          <t>NT_H_008</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D65" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E58" s="1" t="inlineStr">
+      <c r="E65" s="1" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F58" s="1" t="inlineStr">
-        <is>
-          <t>"Modulo m graph paper" consists of a grid of m^2 points, representing
-all pairs of integer residues (x,y) where 0≤ x&lt;m. To graph a
-congruence on modulo m graph paper, we mark every point (x,y) that
-satisfies the congruence. For example, a graph of y\equiv x^2\pmod 5
-would consist of the points (0,0), (1,1), (2,4), (3,4), and (4,1). The
-graphs of y\equiv 5x+2\pmod16and y\equiv 11x+12\pmod16on modulo 16
-graph paper have some points in common. What is the sum of the
-x-coordinates of those points?</t>
-        </is>
-      </c>
-      <c r="G58" s="1" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>We are looking for pairs (x,y) that satisfy both y\equiv 5x+2 and y\equiv 11x+12\pmod16.
-Thus, the x-coordinates in all such pairs satisfy 5x+2 \equiv 11x+12\pmod16.Subtracting
-5x+2 from both sides of this congruence, we have 0 \equiv 6x+10\pmod16,which is equivalent
-to 0 \equiv 6x-6\pmod16(since 10\equiv -6\pmod16). Thus the solutions we seek are values x
-in the range 0≤ x&lt;16 such that 16 divides 6(x-1). The solutions are x=1, x=9, so the sum
-of x-coordinates is 1+9=10. (As a check, note that the pairs (1,7) and (9,15) satisfy both
-of the original congruences, so these are the points shared by the two graphs.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="90" customHeight="1">
-      <c r="A59" s="1" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>NT_H_008</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="inlineStr">
+      <c r="F65" s="1" t="inlineStr">
+        <is>
+          <t>Find the sum of all positive integers n such that n + 2 divides the
+product 3(n + 3)(n^2 + 9).</t>
+        </is>
+      </c>
+      <c r="G65" s="1" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="H65" s="1" t="inlineStr"/>
+    </row>
+    <row r="66" ht="36" customHeight="1">
+      <c r="A66" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>NT_H_009</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D66" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E59" s="1" t="inlineStr">
+      <c r="E66" s="1" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F59" s="1" t="inlineStr">
-        <is>
-          <t>A book has 136 pages. Each page has the same number of words, and each
-page has no more than 100 words on it. The number of words in the book
-is congruent to 184, modulo 203. How many words are on each page?</t>
-        </is>
-      </c>
-      <c r="G59" s="1" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>If there are p words on each page, then we are given 136p \equiv 184 \pmod203. We can
-divide both sides of the congruence by 8 since 8 is relatively prime to 203, and this
-yields 17p \equiv 23 \pmod203. Checking integers which are 1 more than multiples of 203,
-we find that the modular inverse of 17 modulo 203 is 12. Therefore, p \equiv 12(23) \equiv
-73 \pmod203. Therefore, each page has 73 words on it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="108" customHeight="1">
-      <c r="A60" s="1" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>NT_H_009</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
+      <c r="F66" s="1" t="inlineStr">
+        <is>
+          <t>Find the number of integers less than or equal to 100 that are equal
+to a + b + ab for some choice of distinct positive integers a and b.</t>
+        </is>
+      </c>
+      <c r="G66" s="1" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H66" s="1" t="inlineStr"/>
+    </row>
+    <row r="67" ht="54" customHeight="1">
+      <c r="A67" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="1" t="inlineStr">
+        <is>
+          <t>NT_H_010</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D67" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E60" s="1" t="inlineStr">
+      <c r="E67" s="1" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F60" s="1" t="inlineStr">
-        <is>
-          <t>A certain integer has 4 digits when written in base 8. The same
-integer has d digits when written in base 2. What is the sum of all
-possible values of d?</t>
-        </is>
-      </c>
-      <c r="G60" s="1" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>The smallest integer that has 4 digits in base 8 is 1000_8, which stands for 8^3 = 2^9.
-The largest integer that has 4 digits in base 8 is 7777_8, which is 1 less than 10000_8
-and therefore stands for 8^4-1 = 2^12-1. Thus, when a 4-digit base-8 integer is written in
-base 2, its highest place value is either 2^9, 2^10, or 2^11. It follows that the base-2
-expression has 10, 11, or 12 digits, so the sum of all possible values for d is 10+11+12 =
-33.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="90" customHeight="1">
-      <c r="A61" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>NT_H_010</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="inlineStr">
+      <c r="F67" s="1" t="inlineStr">
+        <is>
+          <t>Let N be the number of positive integer divisors of 17017^17 that
+leave a remainder of 5 upon division by 12. Find the remainder when N
+is divided by 1000.</t>
+        </is>
+      </c>
+      <c r="G67" s="1" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="H67" s="1" t="inlineStr"/>
+    </row>
+    <row r="68" ht="90" customHeight="1">
+      <c r="A68" s="1" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="1" t="inlineStr">
+        <is>
+          <t>NT_H_011</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="inlineStr">
+        <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D68" s="1" t="inlineStr">
         <is>
           <t>Number Theory</t>
         </is>
       </c>
-      <c r="E61" s="1" t="inlineStr">
+      <c r="E68" s="1" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F61" s="1" t="inlineStr">
-        <is>
-          <t>A number is divisible by 9 if the sum of its digits is divisible by 9.
-For example, the number 19836 is divisible by 9 but 19825 is not. If
-D767E89 is divisible by 9, where D and E each represent a single
-digit, what is the sum of all possible values of the sum D+E?</t>
-        </is>
-      </c>
-      <c r="G61" s="1" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>For D767E89 to be divisible by 9, we must have D+7+6+7+E+8+9 = 37+D+E divisible by 9.
-Since D and E are each a single digit, we know each is between 0 and 9. Therefore, D+E is
-between 0 and 18. Therefore, 37+D+E is between 37 and 55. The numbers between 37 and 55
-that are divisible by 9 are 45 and 54. If 37+D+E=45, then D+E=8. If 37+D+E=54, then
-D+E=17. Therefore, the possible values of D+E are 8 and 17. Our answer is then 8+17=25.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="144" customHeight="1">
-      <c r="A62" s="1" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="1" t="inlineStr">
+      <c r="F68" s="1" t="inlineStr">
+        <is>
+          <t>For each positive integer n let f(n) be the value of the base-ten
+numeral n viewed in base b, where b is the least integer greater than
+the greatest digit in n. For example, if n = 72, then b = 8, and 72 as
+a numeral in base 8 equals 7*8 + 2 = 58; therefore f(72) = 58. Find
+the number of positive integers n less than 1000 such that f(n) = n.</t>
+        </is>
+      </c>
+      <c r="G68" s="1" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="H68" s="1" t="inlineStr"/>
+    </row>
+    <row r="69" ht="144" customHeight="1">
+      <c r="A69" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="1" t="inlineStr">
         <is>
           <t>PROB_E_001</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D62" s="1" t="inlineStr">
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D69" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="E62" s="1" t="inlineStr">
+      <c r="E69" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F62" s="1" t="inlineStr">
+      <c r="F69" s="1" t="inlineStr">
         <is>
           <t>A bag contains ten balls, some of which are red and the rest of which
 are yellow. When two balls are drawn at random at the same time, the
@@ -3219,12 +3389,12 @@
 bag are red?</t>
         </is>
       </c>
-      <c r="G62" s="1" t="inlineStr">
+      <c r="G69" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H69" s="1" t="inlineStr">
         <is>
           <t>Let r represent the number of red balls in the bag. The probability that the first ball is
 red is (r/10), while the probability that the other ball is red becomes (r-1/9) (drawing
@@ -3237,74 +3407,74 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="54" customHeight="1">
-      <c r="A63" s="1" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="1" t="inlineStr">
+    <row r="70" ht="54" customHeight="1">
+      <c r="A70" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="1" t="inlineStr">
         <is>
           <t>PROB_E_002</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D63" s="1" t="inlineStr">
+      <c r="C70" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D70" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="E63" s="1" t="inlineStr">
+      <c r="E70" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F63" s="1" t="inlineStr">
+      <c r="F70" s="1" t="inlineStr">
         <is>
           <t>A bag has 3 red marbles and 5 white marbles. Two marbles are drawn
 from the bag and not replaced. What is the probability that the first
 marble is red and the second marble is white?</t>
         </is>
       </c>
-      <c r="G63" s="1" t="inlineStr">
+      <c r="G70" s="1" t="inlineStr">
         <is>
           <t>\dfrac{15}{56}</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H70" s="1" t="inlineStr">
         <is>
           <t>The probability that the first is red is \dfrac38. Now with 7 remaining, the probability
 that the second is white is \dfrac57. The answer is \dfrac38 × \dfrac57 = \dfrac1556.</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="108" customHeight="1">
-      <c r="A64" s="1" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" s="1" t="inlineStr">
+    <row r="71" ht="108" customHeight="1">
+      <c r="A71" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="1" t="inlineStr">
         <is>
           <t>PROB_E_003</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D64" s="1" t="inlineStr">
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D71" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="E64" s="1" t="inlineStr">
+      <c r="E71" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F64" s="1" t="inlineStr">
+      <c r="F71" s="1" t="inlineStr">
         <is>
           <t>A board game spinner is divided into four regions labeled A, B, C, and
 D. The probability of the arrow stopping on region A is (3/8), the
@@ -3314,12 +3484,12 @@
 Express your answer as a common fraction.</t>
         </is>
       </c>
-      <c r="G64" s="1" t="inlineStr">
+      <c r="G71" s="1" t="inlineStr">
         <is>
           <t>\frac{3}{16}</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H71" s="1" t="inlineStr">
         <is>
           <t>Let x be the probability that we want. Since the sum of the four probabilities is 1, we
 have the equation 1 = (3/8) + (1/4) + x + x = (5/8) + 2x. Solving the equation 1=(5/8) +
@@ -3327,31 +3497,31 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="90" customHeight="1">
-      <c r="A65" s="1" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" s="1" t="inlineStr">
+    <row r="72" ht="90" customHeight="1">
+      <c r="A72" s="1" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="1" t="inlineStr">
         <is>
           <t>PROB_E_004</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D65" s="1" t="inlineStr">
+      <c r="C72" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D72" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="E65" s="1" t="inlineStr">
+      <c r="E72" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F65" s="1" t="inlineStr">
+      <c r="F72" s="1" t="inlineStr">
         <is>
           <t>A board game spinner is divided into three parts labeled A, B and C.
 The probability of the spinner landing on A is (1/3) and the
@@ -3360,12 +3530,12 @@
 common fraction.</t>
         </is>
       </c>
-      <c r="G65" s="1" t="inlineStr">
+      <c r="G72" s="1" t="inlineStr">
         <is>
           <t>\frac{1}{4}</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H72" s="1" t="inlineStr">
         <is>
           <t>The spinner is guaranteed to land on exactly one of the three regions, so we know that the
 sum of the probabilities of it landing in each region will be 1. If we let the probability
@@ -3374,43 +3544,43 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="54" customHeight="1">
-      <c r="A66" s="1" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="1" t="inlineStr">
+    <row r="73" ht="54" customHeight="1">
+      <c r="A73" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="1" t="inlineStr">
         <is>
           <t>PROB_E_005</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D66" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D73" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="E66" s="1" t="inlineStr">
+      <c r="E73" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F66" s="1" t="inlineStr">
+      <c r="F73" s="1" t="inlineStr">
         <is>
           <t>A box contains 5 white balls and 6 black balls. Two balls are drawn
 out of the box at random. What is the probability that they both are
 white?</t>
         </is>
       </c>
-      <c r="G66" s="1" t="inlineStr">
+      <c r="G73" s="1" t="inlineStr">
         <is>
           <t>\dfrac{2}{11}</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H73" s="1" t="inlineStr">
         <is>
           <t>There are \binom112 = 55 combinations of two balls that can be drawn. There are \binom52 =
 10 combinations of two white balls that can be drawn. So the probability that two balls
@@ -3418,42 +3588,42 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="54" customHeight="1">
-      <c r="A67" s="1" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" s="1" t="inlineStr">
+    <row r="74" ht="54" customHeight="1">
+      <c r="A74" s="1" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="1" t="inlineStr">
         <is>
           <t>PROB_E_006</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D74" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="E67" s="1" t="inlineStr">
+      <c r="E74" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F67" s="1" t="inlineStr">
+      <c r="F74" s="1" t="inlineStr">
         <is>
           <t>A club has 10 members, 5 boys and 5 girls. Two of the members are
 chosen at random. What is the probability that they are both girls?</t>
         </is>
       </c>
-      <c r="G67" s="1" t="inlineStr">
+      <c r="G74" s="1" t="inlineStr">
         <is>
           <t>\dfrac{2}{9}</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H74" s="1" t="inlineStr">
         <is>
           <t>There are \binom102 = 45 ways to choose two members of the group, and there are \binom52 =
 10 ways to choose two girls. Therefore, the probability that two members chosen at random
@@ -3461,31 +3631,31 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="72" customHeight="1">
-      <c r="A68" s="1" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" s="1" t="inlineStr">
+    <row r="75" ht="72" customHeight="1">
+      <c r="A75" s="1" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="1" t="inlineStr">
         <is>
           <t>PROB_E_007</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D68" s="1" t="inlineStr">
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D75" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="E68" s="1" t="inlineStr">
+      <c r="E75" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F68" s="1" t="inlineStr">
+      <c r="F75" s="1" t="inlineStr">
         <is>
           <t>A jar contains two red marbles, three green marbles, ten white marbles
 and no other marbles. Two marbles are randomly drawn from this jar
@@ -3493,12 +3663,12 @@
 drawn will both be red? Express your answer as a common fraction.</t>
         </is>
       </c>
-      <c r="G68" s="1" t="inlineStr">
+      <c r="G75" s="1" t="inlineStr">
         <is>
           <t>\frac{1}{105}</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H75" s="1" t="inlineStr">
         <is>
           <t>The total number of marbles is 2+3+10=15. The probability that the first marble drawn will
 be red is 2/15. Then, there will be one red left, out of 14. Therefore, the probability of
@@ -3506,31 +3676,31 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="108" customHeight="1">
-      <c r="A69" s="1" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" s="1" t="inlineStr">
+    <row r="76" ht="108" customHeight="1">
+      <c r="A76" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="1" t="inlineStr">
         <is>
           <t>PROB_E_008</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D76" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="E69" s="1" t="inlineStr">
+      <c r="E76" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F69" s="1" t="inlineStr">
+      <c r="F76" s="1" t="inlineStr">
         <is>
           <t>Allison, Brian and Noah each have a 6-sided cube. All of the faces on
 Allison's cube have a 5. The faces on Brian's cube are numbered 1, 2,
@@ -3540,12 +3710,12 @@
 Noah's? Express your answer as a common fraction.</t>
         </is>
       </c>
-      <c r="G69" s="1" t="inlineStr">
+      <c r="G76" s="1" t="inlineStr">
         <is>
           <t>\frac{1}{3}</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H76" s="1" t="inlineStr">
         <is>
           <t>Since Allison will always roll a 5, we must calculate the probability that both Brian and
 Noah roll a 4 or lower. The probability of Brian rolling a 4 or lower is (4/6) = (2/3)
@@ -3556,43 +3726,43 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="54" customHeight="1">
-      <c r="A70" s="1" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" s="1" t="inlineStr">
+    <row r="77" ht="54" customHeight="1">
+      <c r="A77" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="1" t="inlineStr">
         <is>
           <t>PROB_E_009</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D70" s="1" t="inlineStr">
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D77" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="E70" s="1" t="inlineStr">
+      <c r="E77" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F70" s="1" t="inlineStr">
+      <c r="F77" s="1" t="inlineStr">
         <is>
           <t>James has 7 apples. 4 of them are red, and 3 of them are green. If he
 chooses 2 apples at random, what is the probability that both the
 apples he chooses are green?</t>
         </is>
       </c>
-      <c r="G70" s="1" t="inlineStr">
+      <c r="G77" s="1" t="inlineStr">
         <is>
           <t>\frac{1}{7}</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H77" s="1" t="inlineStr">
         <is>
           <t>There are \binom72=21 total ways for James to choose 2 apples from 7, but only \binom32=3
 ways for him to choose 2 green apples. So, the probability that he chooses 2 green apples
@@ -3600,31 +3770,31 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="162" customHeight="1">
-      <c r="A71" s="1" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" s="1" t="inlineStr">
+    <row r="78" ht="162" customHeight="1">
+      <c r="A78" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="1" t="inlineStr">
         <is>
           <t>PROB_E_010</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D71" s="1" t="inlineStr">
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D78" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="E71" s="1" t="inlineStr">
+      <c r="E78" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F71" s="1" t="inlineStr">
+      <c r="F78" s="1" t="inlineStr">
         <is>
           <t>Keisha's basketball team must decide on a new uniform. The seventh-
 graders will pick the color of the shorts (black or gold) and the
@@ -3635,12 +3805,12 @@
 the jersey? Express your answer as a common fraction.</t>
         </is>
       </c>
-      <c r="G71" s="1" t="inlineStr">
+      <c r="G78" s="1" t="inlineStr">
         <is>
           <t>\frac{2}{3}</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H78" s="1" t="inlineStr">
         <is>
           <t>We will count the number of garment configurations in which the garments do not match
 color and divide by the total number of garment configurations in order to find the
@@ -3654,42 +3824,42 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="54" customHeight="1">
-      <c r="A72" s="1" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" s="1" t="inlineStr">
+    <row r="79" ht="54" customHeight="1">
+      <c r="A79" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="1" t="inlineStr">
         <is>
           <t>PROB_M_001</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D72" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D79" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="E72" s="1" t="inlineStr">
+      <c r="E79" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F72" s="1" t="inlineStr">
+      <c r="F79" s="1" t="inlineStr">
         <is>
           <t>2 distinct vertices of an octagon are chosen at random. What is the
 probability that they are adjacent?</t>
         </is>
       </c>
-      <c r="G72" s="1" t="inlineStr">
+      <c r="G79" s="1" t="inlineStr">
         <is>
           <t>\frac{2}{7}</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H79" s="1" t="inlineStr">
         <is>
           <t>After we choose the first vertex, there are 7 ways to choose the second. There are only 2
 of these that are adjacent to the first vertex, so the probability the two vertices are
@@ -3697,31 +3867,31 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="72" customHeight="1">
-      <c r="A73" s="1" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" s="1" t="inlineStr">
+    <row r="80" ht="72" customHeight="1">
+      <c r="A80" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="1" t="inlineStr">
         <is>
           <t>PROB_M_002</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="inlineStr">
+      <c r="C80" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D80" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="E73" s="1" t="inlineStr">
+      <c r="E80" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F73" s="1" t="inlineStr">
+      <c r="F80" s="1" t="inlineStr">
         <is>
           <t>A bag contains 10 red marbles and 6 blue marbles. Three marbles are
 selected at random and without replacement. What is the probability
@@ -3729,12 +3899,12 @@
 common fraction.</t>
         </is>
       </c>
-      <c r="G73" s="1" t="inlineStr">
+      <c r="G80" s="1" t="inlineStr">
         <is>
           <t>\frac{15}{56}</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H80" s="1" t="inlineStr">
         <is>
           <t>There are three ways to draw two blue marbles and a red one: RBB, BRB, and BBR. Since
 there are no overlapping outcomes, these are distinct cases and their sum is the total
@@ -3743,31 +3913,31 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="126" customHeight="1">
-      <c r="A74" s="1" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" s="1" t="inlineStr">
+    <row r="81" ht="126" customHeight="1">
+      <c r="A81" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="1" t="inlineStr">
         <is>
           <t>PROB_M_003</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D74" s="1" t="inlineStr">
+      <c r="C81" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D81" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="E74" s="1" t="inlineStr">
+      <c r="E81" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F74" s="1" t="inlineStr">
+      <c r="F81" s="1" t="inlineStr">
         <is>
           <t>A bag contains 3 tan, 2 pink and 4 violet chips. If the 9 chips are
 randomly drawn from the bag, one at a time and without replacement,
@@ -3778,12 +3948,12 @@
 common fraction.</t>
         </is>
       </c>
-      <c r="G74" s="1" t="inlineStr">
+      <c r="G81" s="1" t="inlineStr">
         <is>
           <t>\frac{1}{210}</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H81" s="1" t="inlineStr">
         <is>
           <t>We count the number of ways to draw the tan chips consecutively, the pink chips
 consecutively, and the violet chips consecutively (although not necessarily in that
@@ -3794,43 +3964,43 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="54" customHeight="1">
-      <c r="A75" s="1" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" s="1" t="inlineStr">
+    <row r="82" ht="54" customHeight="1">
+      <c r="A82" s="1" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="1" t="inlineStr">
         <is>
           <t>PROB_M_004</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="inlineStr">
+      <c r="C82" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D82" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="E75" s="1" t="inlineStr">
+      <c r="E82" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F75" s="1" t="inlineStr">
+      <c r="F82" s="1" t="inlineStr">
         <is>
           <t>A bag has 4 red marbles, 5 white marbles, and 6 blue marbles. Three
 marbles are drawn from the bag (without replacement). What is the
 probability that they are all the same color?</t>
         </is>
       </c>
-      <c r="G75" s="1" t="inlineStr">
+      <c r="G82" s="1" t="inlineStr">
         <is>
           <t>\frac{34}{455}</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H82" s="1" t="inlineStr">
         <is>
           <t>We can have all red, all white, or all blue. Thus the answer is \beginalign* &amp;P(\textall
 red) + P(\textall white) + P(\textall blue) \\ &amp; = ((4/15)×(3/14)×(2/13))
@@ -3838,43 +4008,43 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="108" customHeight="1">
-      <c r="A76" s="1" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" s="1" t="inlineStr">
+    <row r="83" ht="108" customHeight="1">
+      <c r="A83" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="1" t="inlineStr">
         <is>
           <t>PROB_M_005</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D76" s="1" t="inlineStr">
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D83" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="E76" s="1" t="inlineStr">
+      <c r="E83" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F76" s="1" t="inlineStr">
+      <c r="F83" s="1" t="inlineStr">
         <is>
           <t>A box contains 4 white balls and 4 black balls. I draw them out of the
 box, one at a time. What is the probability that all of my draws
 alternate colors?</t>
         </is>
       </c>
-      <c r="G76" s="1" t="inlineStr">
+      <c r="G83" s="1" t="inlineStr">
         <is>
           <t>\dfrac{1}{35}</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H83" s="1" t="inlineStr">
         <is>
           <t>Let B denote drawing a black ball and W denote drawing a white ball. There are two
 possible successful orders: BWBWBWBW or WBWBWBWB. There are \binom84 = 70 ways to arrange
@@ -3885,43 +4055,43 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="54" customHeight="1">
-      <c r="A77" s="1" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" s="1" t="inlineStr">
+    <row r="84" ht="54" customHeight="1">
+      <c r="A84" s="1" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="1" t="inlineStr">
         <is>
           <t>PROB_M_006</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D84" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="E77" s="1" t="inlineStr">
+      <c r="E84" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F77" s="1" t="inlineStr">
+      <c r="F84" s="1" t="inlineStr">
         <is>
           <t>A box contains 5 white balls and 6 black balls. Five balls are drawn
 out of the box at random. What is the probability that they all are
 white?</t>
         </is>
       </c>
-      <c r="G77" s="1" t="inlineStr">
+      <c r="G84" s="1" t="inlineStr">
         <is>
           <t>\dfrac{1}{462}</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H84" s="1" t="inlineStr">
         <is>
           <t>There are \binom115 = 462 ways to choose 5 balls out of the box. There is only \binom55 =
 1 way to choose 5 white balls out of 5. This means that the probability that all 5 balls
@@ -3929,42 +4099,42 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="162" customHeight="1">
-      <c r="A78" s="1" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" s="1" t="inlineStr">
+    <row r="85" ht="162" customHeight="1">
+      <c r="A85" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="1" t="inlineStr">
         <is>
           <t>PROB_M_007</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
+      <c r="C85" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D85" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="E78" s="1" t="inlineStr">
+      <c r="E85" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F78" s="1" t="inlineStr">
+      <c r="F85" s="1" t="inlineStr">
         <is>
           <t>A fair coin is flipped 7 times. What is the probability that at least
 5 of the flips come up heads?</t>
         </is>
       </c>
-      <c r="G78" s="1" t="inlineStr">
+      <c r="G85" s="1" t="inlineStr">
         <is>
           <t>\frac{29}{128}</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H85" s="1" t="inlineStr">
         <is>
           <t>First, we count the number of total outcomes. Each toss has 2 possibilities - heads or
 tails - so the 7 tosses have 2^7 = 128 possible outcomes. To count the number of outcomes
@@ -3978,43 +4148,43 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="126" customHeight="1">
-      <c r="A79" s="1" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" s="1" t="inlineStr">
+    <row r="86" ht="126" customHeight="1">
+      <c r="A86" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="1" t="inlineStr">
         <is>
           <t>PROB_M_008</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D86" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="E79" s="1" t="inlineStr">
+      <c r="E86" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F79" s="1" t="inlineStr">
+      <c r="F86" s="1" t="inlineStr">
         <is>
           <t>A fair coin is tossed six times and the sequence of heads and tails is
 recorded. What is the probability that the sequence contains exactly
 two heads? Express your answer as a common fraction.</t>
         </is>
       </c>
-      <c r="G79" s="1" t="inlineStr">
+      <c r="G86" s="1" t="inlineStr">
         <is>
           <t>\frac{15}{64}</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H86" s="1" t="inlineStr">
         <is>
           <t>There are a total of 2^6=64 equally likely sequences of heads and tails we could record
 from the fair coin, since heads and tails are equally likely for each of the six tosses.
@@ -4026,43 +4196,43 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="180" customHeight="1">
-      <c r="A80" s="1" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" s="1" t="inlineStr">
+    <row r="87" ht="180" customHeight="1">
+      <c r="A87" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="1" t="inlineStr">
         <is>
           <t>PROB_M_009</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D87" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="E80" s="1" t="inlineStr">
+      <c r="E87" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F80" s="1" t="inlineStr">
+      <c r="F87" s="1" t="inlineStr">
         <is>
           <t>A point (x,y) is randomly and uniformly chosen inside the square with
 vertices (0,0), (0,2), (2,2), and (2,0). What is the probability that
 x+y &lt; 3?</t>
         </is>
       </c>
-      <c r="G80" s="1" t="inlineStr">
+      <c r="G87" s="1" t="inlineStr">
         <is>
           <t>\dfrac{7}{8}</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H87" s="1" t="inlineStr">
         <is>
           <t>We note that the points for which x+y&lt;3 are those that lie below the line x+y = 3, or y=
 -x + 3. As the diagram below illustrates, these are all the points in the square except
@@ -4077,43 +4247,43 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="126" customHeight="1">
-      <c r="A81" s="1" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" s="1" t="inlineStr">
+    <row r="88" ht="126" customHeight="1">
+      <c r="A88" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="1" t="inlineStr">
         <is>
           <t>PROB_M_010</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D88" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="E81" s="1" t="inlineStr">
+      <c r="E88" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F81" s="1" t="inlineStr">
+      <c r="F88" s="1" t="inlineStr">
         <is>
           <t>A point (x,y) is randomly picked from inside the rectangle with
 vertices (0,0), (3,0), (3,2), and (0,2). What is the probability that
 x &lt; y?</t>
         </is>
       </c>
-      <c r="G81" s="1" t="inlineStr">
+      <c r="G88" s="1" t="inlineStr">
         <is>
           <t>\dfrac{1}{3}</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H88" s="1" t="inlineStr">
         <is>
           <t>The point (x,y) satisfies x &lt; y if and only if it belongs to the shaded triangle bounded
 by the lines x=y, y=2, and x=0, the area of which is 2. The rectangle has area 6, so the
@@ -4125,202 +4295,285 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="90" customHeight="1">
-      <c r="A82" s="1" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" s="1" t="inlineStr">
+    <row r="89" ht="108" customHeight="1">
+      <c r="A89" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="1" t="inlineStr">
         <is>
           <t>PROB_H_001</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
+      <c r="C89" s="1" t="inlineStr">
         <is>
           <t>AIME</t>
         </is>
       </c>
-      <c r="D82" s="1" t="inlineStr">
+      <c r="D89" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="E82" s="1" t="inlineStr">
+      <c r="E89" s="1" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F82" s="1" t="inlineStr">
-        <is>
-          <t>11. Each vertex of a regular octagon is independently colored either
-red or blue with equal probability. The probability that the octagon
-can then be rotated so that all of the blue vertices end up at
-positions where there had been red vertices is m, where m and n n are
-relatively prime positive integers. Find m + n.</t>
-        </is>
-      </c>
-      <c r="G82" s="1" t="inlineStr">
+      <c r="F89" s="1" t="inlineStr">
+        <is>
+          <t>Jen enters a lottery by selecting 4 distinct elements of S =
+{1,2,3,...,9,10}. Then four elements of S are drawn at random. Jen
+wins a prize if at least two of her numbers were drawn, and wins the
+grand prize if all four of her numbers were drawn. The probability
+that Jen wins the grand prize given that Jen wins a prize is m/n where
+m and n are relatively prime positive integers. Find m + n.</t>
+        </is>
+      </c>
+      <c r="G89" s="1" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="H89" s="1" t="inlineStr"/>
+    </row>
+    <row r="90" ht="90" customHeight="1">
+      <c r="A90" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="1" t="inlineStr">
+        <is>
+          <t>PROB_H_002</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="inlineStr">
+        <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D90" s="1" t="inlineStr">
+        <is>
+          <t>Probability</t>
+        </is>
+      </c>
+      <c r="E90" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F90" s="1" t="inlineStr">
+        <is>
+          <t>Each vertex of a regular octagon is independently colored either red
+or blue with equal probability. The probability that the octagon can
+then be rotated so that all of the blue vertices end up at positions
+where there had been red vertices is m/n, where m and n are relatively
+prime positive integers. Find m + n.</t>
+        </is>
+      </c>
+      <c r="G90" s="1" t="inlineStr">
         <is>
           <t>371</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83" ht="108" customHeight="1">
-      <c r="A83" s="1" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>PROB_H_002</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="H90" s="1" t="inlineStr"/>
+    </row>
+    <row r="91" ht="126" customHeight="1">
+      <c r="A91" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="1" t="inlineStr">
+        <is>
+          <t>PROB_H_003</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="inlineStr">
         <is>
           <t>AIME</t>
         </is>
       </c>
-      <c r="D83" s="1" t="inlineStr">
+      <c r="D91" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="E83" s="1" t="inlineStr">
+      <c r="E91" s="1" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F83" s="1" t="inlineStr">
-        <is>
-          <t>7. A standard fair six-sided die is rolled repeatedly. Each time the
-die reads 1 or 2, Alice gets a coin; each time it reads 3 or 4, Bob
-gets a coin; and each time it reads 5 or 6, Carol gets a coin. The
-probability that Alice and Bob each receive at least two coins before
-Carol receives any coins can be written as m, where m and n are
-relatively n prime positive integers. Find 100m + n.</t>
-        </is>
-      </c>
-      <c r="G83" s="1" t="inlineStr">
-        <is>
-          <t>754</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84" ht="198" customHeight="1">
-      <c r="A84" s="1" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>PROB_H_003</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
+      <c r="F91" s="1" t="inlineStr">
+        <is>
+          <t>The twelve letters A,B,C,D,E,F,G,H,I,J,K, and L are randomly grouped
+into six pairs of letters. The two letters in each pair are placed
+next to each other in alphabetical order to form six two-letter words,
+and then those six words are listed alphabetically. For example, a
+possible result is AB,CJ,DG,EK,FL,HI. The probability that the last
+word listed contains G is m/n, where m and n are relatively prime
+positive integers. Find m + n.</t>
+        </is>
+      </c>
+      <c r="G91" s="1" t="inlineStr">
+        <is>
+          <t>821</t>
+        </is>
+      </c>
+      <c r="H91" s="1" t="inlineStr"/>
+    </row>
+    <row r="92" ht="108" customHeight="1">
+      <c r="A92" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="1" t="inlineStr">
+        <is>
+          <t>PROB_H_004</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="inlineStr">
         <is>
           <t>AIME</t>
         </is>
       </c>
-      <c r="D84" s="1" t="inlineStr">
+      <c r="D92" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="E84" s="1" t="inlineStr">
+      <c r="E92" s="1" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F84" s="1" t="inlineStr">
-        <is>
-          <t>9. Joanne has a blank fair six-sided die and six stickers each
-displaying a different integer from 1 to 6. Joanne rolls the die and
-then places the sticker labeled 1 on the top face of the die. She then
-rolls the die again, places the sticker labeled 2 on the top face, and
-continues this process to place the rest of the stickers in order. If
-the die ever lands with a sticker already on its top face, the new
-sticker is placed to cover the old sticker. Let p be the conditional
-probability that at the end of the process exactly one face has been
-left blank, given that all the even-numbered stickers are visible on
-faces of the die. Then p can be written as m, where m and n are
-relatively prime positive integers. n Find m + n.</t>
-        </is>
-      </c>
-      <c r="G84" s="1" t="inlineStr">
+      <c r="F92" s="1" t="inlineStr">
+        <is>
+          <t>Alex divides a disk into four quadrants with two perpendicular
+diameters intersecting at the center of the disk. He draws 25 more
+line segments through the disk, drawing each segment by selecting two
+points at random on the perimeter of the disk in different quadrants
+and connecting these two points. Find the expected number of regions
+into which these 27 line segments divide the disk.</t>
+        </is>
+      </c>
+      <c r="G92" s="1" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="H92" s="1" t="inlineStr"/>
+    </row>
+    <row r="93" ht="126" customHeight="1">
+      <c r="A93" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="1" t="inlineStr">
+        <is>
+          <t>PROB_H_005</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="inlineStr">
+        <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D93" s="1" t="inlineStr">
+        <is>
+          <t>Probability</t>
+        </is>
+      </c>
+      <c r="E93" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F93" s="1" t="inlineStr">
+        <is>
+          <t>Suppose triangle ABC has angles angle-BAC = 84 degrees, angle-ABC = 60
+degrees, and angle-ACB = 36 degrees. Let D, E, and F be the midpoints
+of sides BC, AC, and AB, respectively. The circumcircle of triangle
+DEF intersects BD, AE, and AF at points G, H, and J, respectively. The
+points G, D, E, H, J, and F divide the circumcircle of triangle DEF
+into six minor arcs, as shown. Find arc-DE + 2*arc-HJ + 3*arc-FG,
+where the arcs are measured in degrees.</t>
+        </is>
+      </c>
+      <c r="G93" s="1" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="H93" s="1" t="inlineStr"/>
+    </row>
+    <row r="94" ht="198" customHeight="1">
+      <c r="A94" s="1" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="1" t="inlineStr">
+        <is>
+          <t>PROB_H_006</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="inlineStr">
+        <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D94" s="1" t="inlineStr">
+        <is>
+          <t>Probability</t>
+        </is>
+      </c>
+      <c r="E94" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F94" s="1" t="inlineStr">
+        <is>
+          <t>Joanne has a blank fair six-sided die and six stickers each displaying
+a different integer from 1 to 6. Joanne rolls the die and then places
+the sticker labeled 1 on the top face of the die. She then rolls the
+die again, places the sticker labeled 2 on the top face, and continues
+this process to place the rest of the stickers in order. If the die
+ever lands with a sticker already on its top face, the new sticker is
+placed to cover the old sticker. Let p be the conditional probability
+that at the end of the process exactly one face has been left blank,
+given that all the even-numbered stickers are visible on faces of the
+die. Then p can be written as m/n, where m and n are relatively prime
+positive integers. Find m + n.</t>
+        </is>
+      </c>
+      <c r="G94" s="1" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85" ht="126" customHeight="1">
-      <c r="A85" s="1" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>PROB_H_004</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="H94" s="1" t="inlineStr"/>
+    </row>
+    <row r="95" ht="108" customHeight="1">
+      <c r="A95" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="1" t="inlineStr">
+        <is>
+          <t>PROB_H_007</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="inlineStr">
         <is>
           <t>AIME</t>
         </is>
       </c>
-      <c r="D85" s="1" t="inlineStr">
+      <c r="D95" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="E85" s="1" t="inlineStr">
+      <c r="E95" s="1" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F85" s="1" t="inlineStr">
-        <is>
-          <t>7. The twelve letters A,B,C,D,E,F,G,H,I,J,K, and L are randomly
-grouped into six pairs of letters. The two letters in each pair are
-placed next to each other in alphabetical order to form six two-letter
-words, and then those six words are listed alphabetically. For
-example, a possible result is AB,CJ,DG,EK,FL,HI. The probability that
-the last word listed contains G is m, where m and n are relatively n
-prime positive integers. Find m + n.</t>
-        </is>
-      </c>
-      <c r="G85" s="1" t="inlineStr">
-        <is>
-          <t>821</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86" ht="108" customHeight="1">
-      <c r="A86" s="1" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" s="1" t="inlineStr">
-        <is>
-          <t>PROB_H_005</t>
-        </is>
-      </c>
-      <c r="C86" s="1" t="inlineStr">
-        <is>
-          <t>AIME</t>
-        </is>
-      </c>
-      <c r="D86" s="1" t="inlineStr">
-        <is>
-          <t>Probability</t>
-        </is>
-      </c>
-      <c r="E86" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F86" s="1" t="inlineStr">
-        <is>
-          <t>5. An urn contains n marbles. Each marble is either red or blue, and
+      <c r="F95" s="1" t="inlineStr">
+        <is>
+          <t>An urn contains n marbles. Each marble is either red or blue, and
 there are at least 7 marbles of each color. When 7 marbles are drawn
 randomly from the urn without replacement, the probability that
 exactly 4 of them are red equals the probability that exactly 5 of
@@ -4328,283 +4581,91 @@
 this is possible.</t>
         </is>
       </c>
-      <c r="G86" s="1" t="inlineStr">
+      <c r="G95" s="1" t="inlineStr">
         <is>
           <t>190</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87" ht="108" customHeight="1">
-      <c r="A87" s="1" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" s="1" t="inlineStr">
-        <is>
-          <t>PROB_H_006</t>
-        </is>
-      </c>
-      <c r="C87" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D87" s="1" t="inlineStr">
+      <c r="H95" s="1" t="inlineStr"/>
+    </row>
+    <row r="96" ht="108" customHeight="1">
+      <c r="A96" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="1" t="inlineStr">
+        <is>
+          <t>PROB_H_008</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="inlineStr">
+        <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D96" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="E87" s="1" t="inlineStr">
+      <c r="E96" s="1" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F87" s="1" t="inlineStr">
-        <is>
-          <t>4 12-sided dice are rolled. What is the probability that the number of
-dice showing a two digit number is equal to the number of dice showing
-a one digit number? Express your answer as a common fraction. (Assume
-that the numbers on the 12 sides are the numbers from 1 to 12
-expressed in decimal.)</t>
-        </is>
-      </c>
-      <c r="G87" s="1" t="inlineStr">
-        <is>
-          <t>\dfrac{27}{128}</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>Since 9 out of the 12 possible results are one digit numbers, each die will show a one
-digit number with probability of (3/4) and a two digit number with probability of (1/4).
-The probability that two particular dice will show 2 two digit numbers and 2 one digit
-numbers is thus ((1/4))^2((3/4))^2. There are \binom42=6 ways to select which two dice
-will show one digit numbers, so we multiply to get the probability that we want:
-6·((1/4))^2((3/4))^2=\dfrac54256=\dfrac27128.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="54" customHeight="1">
-      <c r="A88" s="1" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>PROB_H_007</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>Probability</t>
-        </is>
-      </c>
-      <c r="E88" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F88" s="1" t="inlineStr">
-        <is>
-          <t>8 coins are simultaneously flipped. What is the probability that heads
-are showing on at most 2 of them?</t>
-        </is>
-      </c>
-      <c r="G88" s="1" t="inlineStr">
-        <is>
-          <t>\dfrac{37}{256}</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>The number of ways for the outcome to have exactly 0, 1, or 2 heads are \binom80=1,
-\binom81=8, or \binom82=28, respectively. There are 2^8 total possible outcomes (2
-possibilities for each coin, and 8 coins). So the answer is \dfrac1+8+282^8=\dfrac37256.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="72" customHeight="1">
-      <c r="A89" s="1" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>PROB_H_008</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>Probability</t>
-        </is>
-      </c>
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F89" s="1" t="inlineStr">
-        <is>
-          <t>A bin has 8 black balls and 7 white balls. 3 of the balls are drawn at
-random. What is the probability of drawing 2 of one color and 1 of the
-other color?</t>
-        </is>
-      </c>
-      <c r="G89" s="1" t="inlineStr">
-        <is>
-          <t>\frac{4}{5}</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>The number of ways to draw out 3 balls from 15 is \binom153=455. We can choose 2 black
-balls and 1 white ball in \binom82\binom71=196 ways. We can pick 1 black ball and 2 white
-balls in \binom81\binom72=168 ways. Therefore we have 196+168=364 ways to satisfy the
-condition, so the answer is \dfrac364455=\frac45.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="90" customHeight="1">
-      <c r="A90" s="1" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" s="1" t="inlineStr">
-        <is>
-          <t>PROB_H_009</t>
-        </is>
-      </c>
-      <c r="C90" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D90" s="1" t="inlineStr">
-        <is>
-          <t>Probability</t>
-        </is>
-      </c>
-      <c r="E90" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F90" s="1" t="inlineStr">
-        <is>
-          <t>A bowl contains 10 jellybeans (four red, one blue and five white). If
-you pick three jellybeans from the bowl at random and without
-replacement, what is the probability that exactly two will be red?
-Express your answer as a common fraction.</t>
-        </is>
-      </c>
-      <c r="G90" s="1" t="inlineStr">
-        <is>
-          <t>\frac{3}{10}</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>First, we consider how many total sets of three jellybeans we can select, which is very
-simply 10 \choose 3 = 120, if we treat all 10 jellybeans as distinct. Now, if we have
-exactly 2 red jellybeans, there are 4 \choose 2 = 6 pairs of red jellybeans, and 5+1 = 6
-choices for the third non-red jellybean. So, there are 6 · 6 = 36 successful outcomes. So
-our probability is (6 · 6/120) = (6/20) = \frac310.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="108" customHeight="1">
-      <c r="A91" s="1" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>PROB_H_010</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>Probability</t>
-        </is>
-      </c>
-      <c r="E91" s="1" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="F91" s="1" t="inlineStr">
-        <is>
-          <t>A box contains six cards. Three of the cards are black on both sides,
-one card is black on one side and red on the other, and two of the
-cards are red on both sides. You pick a card uniformly at random from
-the box and look at a random side. Given that the side you see is red,
-what is the probability that the other side is red? Express your
-answer as a common fraction.</t>
-        </is>
-      </c>
-      <c r="G91" s="1" t="inlineStr">
-        <is>
-          <t>\frac{4}{5}</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>Consider the two different faces of each card as distinct items at first. Since we have
-two completely red cards and one half-red card, we have a total of 5 red card-sides. So,
-since we are looking at a red face, we know we have one of these 5 red card-sides. 4 of
-these are located on a completely red card, and turning it over will reveal another red
-face. So the probability is \frac45.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="54" customHeight="1">
-      <c r="A92" s="1" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" s="1" t="inlineStr">
+      <c r="F96" s="1" t="inlineStr">
+        <is>
+          <t>A standard fair six-sided die is rolled repeatedly. Each time the die
+reads 1 or 2, Alice gets a coin; each time it reads 3 or 4, Bob gets a
+coin; and each time it reads 5 or 6, Carol gets a coin. The
+probability that Alice and Bob each receive at least two coins before
+Carol receives any coins can be written as m/n, where m and n are
+relatively prime positive integers. Find 100m + n.</t>
+        </is>
+      </c>
+      <c r="G96" s="1" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="H96" s="1" t="inlineStr"/>
+    </row>
+    <row r="97" ht="54" customHeight="1">
+      <c r="A97" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="1" t="inlineStr">
         <is>
           <t>COMB_E_001</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D92" s="1" t="inlineStr">
+      <c r="C97" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D97" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E92" s="1" t="inlineStr">
+      <c r="E97" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F92" s="1" t="inlineStr">
+      <c r="F97" s="1" t="inlineStr">
         <is>
           <t>23 people attend a party. Each person shakes hands with at most 22
 other people. What is the maximum possible number of handshakes,
 assuming that any two people can shake hands at most once?</t>
         </is>
       </c>
-      <c r="G92" s="1" t="inlineStr">
+      <c r="G97" s="1" t="inlineStr">
         <is>
           <t>253</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H97" s="1" t="inlineStr">
         <is>
           <t>Note that if each person shakes hands with every other person, then the number of
 handshakes is maximized. There are \binom232 = ((23)(22)/2) = (23)(11) = 230+23 = 253 ways
@@ -4612,84 +4673,84 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="36" customHeight="1">
-      <c r="A93" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" s="1" t="inlineStr">
+    <row r="98" ht="36" customHeight="1">
+      <c r="A98" s="1" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="1" t="inlineStr">
         <is>
           <t>COMB_E_002</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D93" s="1" t="inlineStr">
+      <c r="C98" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D98" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E93" s="1" t="inlineStr">
+      <c r="E98" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F93" s="1" t="inlineStr">
+      <c r="F98" s="1" t="inlineStr">
         <is>
           <t>8 people attend a party. During the party everyone shakes hands with
 everyone else. How many handshakes take place at the party?</t>
         </is>
       </c>
-      <c r="G93" s="1" t="inlineStr">
+      <c r="G98" s="1" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="H98" s="1" t="inlineStr">
         <is>
           <t>We can choose 2 people to shake hands with each other out of a group of 8 people in
 \binom82 = 28 ways.</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="54" customHeight="1">
-      <c r="A94" s="1" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" s="1" t="inlineStr">
+    <row r="99" ht="54" customHeight="1">
+      <c r="A99" s="1" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="1" t="inlineStr">
         <is>
           <t>COMB_E_003</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D94" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D99" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E94" s="1" t="inlineStr">
+      <c r="E99" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F94" s="1" t="inlineStr">
+      <c r="F99" s="1" t="inlineStr">
         <is>
           <t>A Senate committee has 8 Republicans and 6 Democrats. In how many ways
 can we form a subcommittee with 3 Republicans and 2 Democrats?</t>
         </is>
       </c>
-      <c r="G94" s="1" t="inlineStr">
+      <c r="G99" s="1" t="inlineStr">
         <is>
           <t>840</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="H99" s="1" t="inlineStr">
         <is>
           <t>There are 8 Republicans and 3 spots for them, so there are \binom83 = 56 ways to choose
 the Republicans. There are 6 Democrats and 2 spots for them, so there are \binom62 = 15
@@ -4697,42 +4758,42 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="72" customHeight="1">
-      <c r="A95" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" s="1" t="inlineStr">
+    <row r="100" ht="72" customHeight="1">
+      <c r="A100" s="1" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="1" t="inlineStr">
         <is>
           <t>COMB_E_004</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D95" s="1" t="inlineStr">
+      <c r="C100" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D100" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E95" s="1" t="inlineStr">
+      <c r="E100" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F95" s="1" t="inlineStr">
+      <c r="F100" s="1" t="inlineStr">
         <is>
           <t>A palindrome is a number that reads the same forwards and backwards,
 such as 3003. How many positive four-digit integers are palindromes?</t>
         </is>
       </c>
-      <c r="G95" s="1" t="inlineStr">
+      <c r="G100" s="1" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="H100" s="1" t="inlineStr">
         <is>
           <t>Constructing palindromes requires that we choose the thousands digit (which defines the
 units digit) and the hundreds digit (which defines the tens digit). Since there are 9
@@ -4741,117 +4802,117 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="54" customHeight="1">
-      <c r="A96" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" s="1" t="inlineStr">
+    <row r="101" ht="54" customHeight="1">
+      <c r="A101" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="1" t="inlineStr">
         <is>
           <t>COMB_E_005</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D96" s="1" t="inlineStr">
+      <c r="C101" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D101" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E96" s="1" t="inlineStr">
+      <c r="E101" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F96" s="1" t="inlineStr">
+      <c r="F101" s="1" t="inlineStr">
         <is>
           <t>A pizza parlor offers six toppings. What is the greatest number of
 four-topping pizzas that can be made such that no two pizzas have the
 same topping combination?</t>
         </is>
       </c>
-      <c r="G96" s="1" t="inlineStr">
+      <c r="G101" s="1" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="H101" s="1" t="inlineStr">
         <is>
           <t>Because there are 6 choices of toppings, and each pizza must have 4 of them, there are 6
 \choose 4 = 15 four-topping pizzas.</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="54" customHeight="1">
-      <c r="A97" s="1" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" s="1" t="inlineStr">
+    <row r="102" ht="54" customHeight="1">
+      <c r="A102" s="1" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="1" t="inlineStr">
         <is>
           <t>COMB_E_006</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D97" s="1" t="inlineStr">
+      <c r="C102" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D102" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E97" s="1" t="inlineStr">
+      <c r="E102" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F97" s="1" t="inlineStr">
+      <c r="F102" s="1" t="inlineStr">
         <is>
           <t>A yogurt shop sells four flavors of yogurt and has six different
 toppings. How many combinations of one flavor and two different
 toppings are available?</t>
         </is>
       </c>
-      <c r="G97" s="1" t="inlineStr">
+      <c r="G102" s="1" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="H102" s="1" t="inlineStr">
         <is>
           <t>There are 4 choices of flavor, and \binom62=15 ways to choose two of the six toppings. The
 total number of combinations is 4· 15=60.</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="72" customHeight="1">
-      <c r="A98" s="1" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" s="1" t="inlineStr">
+    <row r="103" ht="72" customHeight="1">
+      <c r="A103" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="1" t="inlineStr">
         <is>
           <t>COMB_E_007</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D98" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D103" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E98" s="1" t="inlineStr">
+      <c r="E103" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F98" s="1" t="inlineStr">
+      <c r="F103" s="1" t="inlineStr">
         <is>
           <t>Alex has 10 different kinds of lunch meat and 9 different kinds of
 cheese. If he wants to make a sandwich with one kind of meat and two
@@ -4859,12 +4920,12 @@
 not matter in which order he chooses the two types of cheese.)</t>
         </is>
       </c>
-      <c r="G98" s="1" t="inlineStr">
+      <c r="G103" s="1" t="inlineStr">
         <is>
           <t>360</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="H103" s="1" t="inlineStr">
         <is>
           <t>There are \binom101=10 ways for Alex to choose which kind of lunch meat to put on his
 sandwich, and there are \binom92=36 ways for Alex to choose which kinds of cheese to put
@@ -4872,31 +4933,31 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="72" customHeight="1">
-      <c r="A99" s="1" t="n">
-        <v>98</v>
-      </c>
-      <c r="B99" s="1" t="inlineStr">
+    <row r="104" ht="72" customHeight="1">
+      <c r="A104" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="1" t="inlineStr">
         <is>
           <t>COMB_E_008</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D104" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E99" s="1" t="inlineStr">
+      <c r="E104" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F99" s="1" t="inlineStr">
+      <c r="F104" s="1" t="inlineStr">
         <is>
           <t>An ice cream shop offers 6 kinds of ice cream. What is the greatest
 number of two scoop sundaes that can be made such that each sundae
@@ -4904,55 +4965,55 @@
 combination?</t>
         </is>
       </c>
-      <c r="G99" s="1" t="inlineStr">
+      <c r="G104" s="1" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="H104" s="1" t="inlineStr">
         <is>
           <t>Because there are 6 choices of ice cream and each sundae must consist of 2 of them, there
 are 6 \choose 2 = 15 kinds of two scoop sundaes.</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="180" customHeight="1">
-      <c r="A100" s="1" t="n">
-        <v>99</v>
-      </c>
-      <c r="B100" s="1" t="inlineStr">
+    <row r="105" ht="180" customHeight="1">
+      <c r="A105" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="1" t="inlineStr">
         <is>
           <t>COMB_E_009</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D105" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E100" s="1" t="inlineStr">
+      <c r="E105" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F100" s="1" t="inlineStr">
+      <c r="F105" s="1" t="inlineStr">
         <is>
           <t>Assume we have a calendrical system in which leap years happen every
 four years, no matter what. In a 150-year period, what is the maximum
 possible number of leap years?</t>
         </is>
       </c>
-      <c r="G100" s="1" t="inlineStr">
+      <c r="G105" s="1" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="H105" s="1" t="inlineStr">
         <is>
           <t>Since 150 divided by 4 is 37.5, there are 37 blocks of 4 years in 150 years, plus two
 extra years. If we let one of those two extra years be a leap year, and we have one leap
@@ -4967,31 +5028,31 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="144" customHeight="1">
-      <c r="A101" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="B101" s="1" t="inlineStr">
+    <row r="106" ht="144" customHeight="1">
+      <c r="A106" s="1" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="1" t="inlineStr">
         <is>
           <t>COMB_E_010</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D106" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E101" s="1" t="inlineStr">
+      <c r="E106" s="1" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="F101" s="1" t="inlineStr">
+      <c r="F106" s="1" t="inlineStr">
         <is>
           <t>At a particular school with 43 students, each student takes chemistry,
 biology, or both. The chemistry class is three times as large as the
@@ -4999,12 +5060,12 @@
 are in the chemistry class?</t>
         </is>
       </c>
-      <c r="G101" s="1" t="inlineStr">
+      <c r="G106" s="1" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="H106" s="1" t="inlineStr">
         <is>
           <t>Let x be the number of students in the biology class who aren't in the chemistry class and
 y be the number of students in the chemistry class who aren't in the biology class. Then,
@@ -5017,31 +5078,31 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="108" customHeight="1">
-      <c r="A102" s="1" t="n">
-        <v>101</v>
-      </c>
-      <c r="B102" s="1" t="inlineStr">
+    <row r="107" ht="108" customHeight="1">
+      <c r="A107" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="1" t="inlineStr">
         <is>
           <t>COMB_M_001</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D107" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E102" s="1" t="inlineStr">
+      <c r="E107" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F102" s="1" t="inlineStr">
+      <c r="F107" s="1" t="inlineStr">
         <is>
           <t>A club has 5 members from each of 3 different schools, for a total of
 15 members. How many possible ways are there to arrange a presidency
@@ -5051,12 +5112,12 @@
 schools sends 1 representative.</t>
         </is>
       </c>
-      <c r="G102" s="1" t="inlineStr">
+      <c r="G107" s="1" t="inlineStr">
         <is>
           <t>750</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="H107" s="1" t="inlineStr">
         <is>
           <t>Pick one of the schools as the host. There are \dbinom52=10 ways to select the two
 representatives from that school and \dbinom51 ways to pick a representative from each of
@@ -5066,43 +5127,43 @@
         </is>
       </c>
     </row>
-    <row r="103" ht="72" customHeight="1">
-      <c r="A103" s="1" t="n">
-        <v>102</v>
-      </c>
-      <c r="B103" s="1" t="inlineStr">
+    <row r="108" ht="72" customHeight="1">
+      <c r="A108" s="1" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="1" t="inlineStr">
         <is>
           <t>COMB_M_002</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
+      <c r="C108" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D108" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E103" s="1" t="inlineStr">
+      <c r="E108" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F103" s="1" t="inlineStr">
+      <c r="F108" s="1" t="inlineStr">
         <is>
           <t>A diagonal of a polygon is a segment joining two nonconsecutive
 vertices of the polygon. How many diagonals does a regular octagon
 have?</t>
         </is>
       </c>
-      <c r="G103" s="1" t="inlineStr">
+      <c r="G108" s="1" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="H108" s="1" t="inlineStr">
         <is>
           <t>An n-gon has n(n-3)/2 diagonals. To see this, subtract the n consecutive pairs of vertices
 from the \binomn2 pairs of vertices: \beginalign* \binomn2-n&amp;=(n(n-1)/2)-n \\
@@ -5111,31 +5172,31 @@
         </is>
       </c>
     </row>
-    <row r="104" ht="72" customHeight="1">
-      <c r="A104" s="1" t="n">
-        <v>103</v>
-      </c>
-      <c r="B104" s="1" t="inlineStr">
+    <row r="109" ht="72" customHeight="1">
+      <c r="A109" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="1" t="inlineStr">
         <is>
           <t>COMB_M_003</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D104" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D109" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E104" s="1" t="inlineStr">
+      <c r="E109" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F104" s="1" t="inlineStr">
+      <c r="F109" s="1" t="inlineStr">
         <is>
           <t>A math conference is presenting a lecture series with six different
 lecturers. If Dr. Smith's lecture depends on Dr. Jones's lecture, so
@@ -5143,12 +5204,12 @@
 many orders can the six lecturers be scheduled?</t>
         </is>
       </c>
-      <c r="G104" s="1" t="inlineStr">
+      <c r="G109" s="1" t="inlineStr">
         <is>
           <t>360</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="H109" s="1" t="inlineStr">
         <is>
           <t>There are a total of 6! ways to order the 6 lectures with no restriction. By symmetry,
 exactly half of these will have Dr. Jones's lecture before Dr. Smith's lecture. Thus there
@@ -5156,43 +5217,43 @@
         </is>
       </c>
     </row>
-    <row r="105" ht="108" customHeight="1">
-      <c r="A105" s="1" t="n">
-        <v>104</v>
-      </c>
-      <c r="B105" s="1" t="inlineStr">
+    <row r="110" ht="108" customHeight="1">
+      <c r="A110" s="1" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="1" t="inlineStr">
         <is>
           <t>COMB_M_004</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
+      <c r="C110" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D110" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E105" s="1" t="inlineStr">
+      <c r="E110" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F105" s="1" t="inlineStr">
+      <c r="F110" s="1" t="inlineStr">
         <is>
           <t>A palindrome is an integer that reads the same forward and backward,
 such as 3663. What percent of the palindromes between 100 and 500
 contain at least one 5?</t>
         </is>
       </c>
-      <c r="G105" s="1" t="inlineStr">
+      <c r="G110" s="1" t="inlineStr">
         <is>
           <t>10\%</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="H110" s="1" t="inlineStr">
         <is>
           <t>Since none of the palindromes between 100 and 500 begin with a 5, the only place a 5 can
 appear is in the tens digit. Therefore, there are 4 palindromes between 100 and 500 with a
@@ -5203,74 +5264,74 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="54" customHeight="1">
-      <c r="A106" s="1" t="n">
-        <v>105</v>
-      </c>
-      <c r="B106" s="1" t="inlineStr">
+    <row r="111" ht="54" customHeight="1">
+      <c r="A111" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="1" t="inlineStr">
         <is>
           <t>COMB_M_005</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D111" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E106" s="1" t="inlineStr">
+      <c r="E111" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F106" s="1" t="inlineStr">
+      <c r="F111" s="1" t="inlineStr">
         <is>
           <t>A plane is uniquely determined by three non-collinear points. What is
 the maximum possible number of planes that can be determined by 12
 points in space?</t>
         </is>
       </c>
-      <c r="G106" s="1" t="inlineStr">
+      <c r="G111" s="1" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="H111" s="1" t="inlineStr">
         <is>
           <t>There are \binom123 = 220 ways to pick any 3 points, which we assume to determine a unique
 plane.</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="108" customHeight="1">
-      <c r="A107" s="1" t="n">
-        <v>106</v>
-      </c>
-      <c r="B107" s="1" t="inlineStr">
+    <row r="112" ht="108" customHeight="1">
+      <c r="A112" s="1" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="1" t="inlineStr">
         <is>
           <t>COMB_M_006</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D112" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E107" s="1" t="inlineStr">
+      <c r="E112" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F107" s="1" t="inlineStr">
+      <c r="F112" s="1" t="inlineStr">
         <is>
           <t>A play has two different male roles, two different female roles and
 two different roles that can be either gender. Only a man can be
@@ -5279,12 +5340,12 @@
 roles be assigned?</t>
         </is>
       </c>
-      <c r="G107" s="1" t="inlineStr">
+      <c r="G112" s="1" t="inlineStr">
         <is>
           <t>25200</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="H112" s="1" t="inlineStr">
         <is>
           <t>We start with the most restrictive conditions: the roles that are not open to both men and
 women. First, we will fill the two male roles. There are 5 men, so there are 5 · 4= 20
@@ -5295,42 +5356,42 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="72" customHeight="1">
-      <c r="A108" s="1" t="n">
-        <v>107</v>
-      </c>
-      <c r="B108" s="1" t="inlineStr">
+    <row r="113" ht="72" customHeight="1">
+      <c r="A113" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="1" t="inlineStr">
         <is>
           <t>COMB_M_007</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D113" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E108" s="1" t="inlineStr">
+      <c r="E113" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F108" s="1" t="inlineStr">
+      <c r="F113" s="1" t="inlineStr">
         <is>
           <t>A rectangle has a perimeter of 64 inches and each side has an integer
 length. How many non-congruent rectangles meet these criteria?</t>
         </is>
       </c>
-      <c r="G108" s="1" t="inlineStr">
+      <c r="G113" s="1" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H113" s="1" t="inlineStr">
         <is>
           <t>Call the height h and the width w. We want to find the number of solutions to 2(w+h)=64 or
 w+h=32. The solutions to this are \[ \(1,31),(2,30),\ldots,(16,16),\ldots,(31,1)\. \]
@@ -5339,43 +5400,43 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="72" customHeight="1">
-      <c r="A109" s="1" t="n">
-        <v>108</v>
-      </c>
-      <c r="B109" s="1" t="inlineStr">
+    <row r="114" ht="72" customHeight="1">
+      <c r="A114" s="1" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="1" t="inlineStr">
         <is>
           <t>COMB_M_008</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D114" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E109" s="1" t="inlineStr">
+      <c r="E114" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F109" s="1" t="inlineStr">
+      <c r="F114" s="1" t="inlineStr">
         <is>
           <t>A teacher wants to arrange 3 copies of Introduction to Geometry and 4
 copies of Introduction to Number Theory on a bookshelf. In how many
 ways can he do that?</t>
         </is>
       </c>
-      <c r="G109" s="1" t="inlineStr">
+      <c r="G114" s="1" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="H114" s="1" t="inlineStr">
         <is>
           <t>There are 7 possible locations for the books. The teacher can select 3 of these and place
 the copies of Introduction to Geometry in those spots and then place the copies of
@@ -5384,31 +5445,31 @@
         </is>
       </c>
     </row>
-    <row r="110" ht="90" customHeight="1">
-      <c r="A110" s="1" t="n">
-        <v>109</v>
-      </c>
-      <c r="B110" s="1" t="inlineStr">
+    <row r="115" ht="90" customHeight="1">
+      <c r="A115" s="1" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="1" t="inlineStr">
         <is>
           <t>COMB_M_009</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D115" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E110" s="1" t="inlineStr">
+      <c r="E115" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F110" s="1" t="inlineStr">
+      <c r="F115" s="1" t="inlineStr">
         <is>
           <t>A zealous geologist is sponsoring a contest in which entrants have to
 guess the age of a shiny rock. He offers these clues: the age of the
@@ -5417,12 +5478,12 @@
 for the rock's age?</t>
         </is>
       </c>
-      <c r="G110" s="1" t="inlineStr">
+      <c r="G115" s="1" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="H115" s="1" t="inlineStr">
         <is>
           <t>There are 3 odd digits which can begin the rock's age. For the five remaining spaces, the
 numbers can be arranged in 5! ways. However, because the digit `2' repeats three times, we
@@ -5431,43 +5492,43 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="90" customHeight="1">
-      <c r="A111" s="1" t="n">
-        <v>110</v>
-      </c>
-      <c r="B111" s="1" t="inlineStr">
+    <row r="116" ht="90" customHeight="1">
+      <c r="A116" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="1" t="inlineStr">
         <is>
           <t>COMB_M_010</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
+        <is>
+          <t>Hendrycks</t>
+        </is>
+      </c>
+      <c r="D116" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E111" s="1" t="inlineStr">
+      <c r="E116" s="1" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F111" s="1" t="inlineStr">
+      <c r="F116" s="1" t="inlineStr">
         <is>
           <t>April has four different basil plants and four different tomato
 plants. In how many ways can she arrange the plants in a row if she
 puts all the tomato plants next to each other?</t>
         </is>
       </c>
-      <c r="G111" s="1" t="inlineStr">
+      <c r="G116" s="1" t="inlineStr">
         <is>
           <t>2880</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="H116" s="1" t="inlineStr">
         <is>
           <t>First, consider arranging the four basil plants and the one group of tomato plants (not
 worrying about the order of the tomato plants within the group). There are 5!=120 ways to
@@ -5477,480 +5538,661 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="90" customHeight="1">
-      <c r="A112" s="1" t="n">
-        <v>111</v>
-      </c>
-      <c r="B112" s="1" t="inlineStr">
+    <row r="117" ht="108" customHeight="1">
+      <c r="A117" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="1" t="inlineStr">
         <is>
           <t>COMB_H_001</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>AIME</t>
         </is>
       </c>
-      <c r="D112" s="1" t="inlineStr">
+      <c r="D117" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E112" s="1" t="inlineStr">
+      <c r="E117" s="1" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F112" s="1" t="inlineStr">
-        <is>
-          <t>15. Find the number of ordered 7−tuples (a,a,a,…,a ) having the
-following 1 2 3 7 properties: • a ∈ {1,2,3} for all k. k • a + a + a +
-a + a + a + a is a multiple of 3. 1 2 3 4 5 6 7 • a a a + a a a + a a
-a + a a a + a a a + a a a + a a a is a multiple of 1 2 4 2 3 5 3 4 6 4
-5 7 5 6 1 6 7 2 7 1 3 3.</t>
-        </is>
-      </c>
-      <c r="G112" s="1" t="inlineStr">
-        <is>
-          <t>393</t>
-        </is>
-      </c>
-      <c r="H112" s="2" t="inlineStr"/>
-    </row>
-    <row r="113" ht="90" customHeight="1">
-      <c r="A113" s="1" t="n">
-        <v>112</v>
-      </c>
-      <c r="B113" s="1" t="inlineStr">
+      <c r="F117" s="1" t="inlineStr">
+        <is>
+          <t>Alice and Bob play the following game. A stack of n tokens lies before
+them. The players take turns with Alice going first. On each turn, the
+player removes 1 token or 4 tokens from the stack. The player who
+removes the last token wins. Find the number of positive integers n
+less than or equal to 2024 such that there is a strategy that
+guarantees that Bob wins, regardless of Alice's moves.</t>
+        </is>
+      </c>
+      <c r="G117" s="1" t="inlineStr">
+        <is>
+          <t>809</t>
+        </is>
+      </c>
+      <c r="H117" s="1" t="inlineStr"/>
+    </row>
+    <row r="118" ht="108" customHeight="1">
+      <c r="A118" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="1" t="inlineStr">
         <is>
           <t>COMB_H_002</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C118" s="1" t="inlineStr">
         <is>
           <t>AIME</t>
         </is>
       </c>
-      <c r="D113" s="1" t="inlineStr">
+      <c r="D118" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E113" s="1" t="inlineStr">
+      <c r="E118" s="1" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F113" s="1" t="inlineStr">
-        <is>
-          <t>14. For integers a and b, let a ∘ b = a − b if a is odd and b is even,
-and a ∘ b = a + b otherwise. Find the number of sequences a,a,a,…,a of
-positive integers such 1 2 3 n that a + a + a + ⋯ + a = 12 and a ∘ a ∘
-a ∘ ⋯ ∘ a = 0, 1 2 3 n 1 2 3 n where the operations are performed from
-left to right; that is, a ∘ a ∘ a means 1 2 3 (a ∘ a ) ∘ a. 1 2 3</t>
-        </is>
-      </c>
-      <c r="G113" s="1" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr"/>
-    </row>
-    <row r="114" ht="270" customHeight="1">
-      <c r="A114" s="1" t="n">
-        <v>113</v>
-      </c>
-      <c r="B114" s="1" t="inlineStr">
+      <c r="F118" s="1" t="inlineStr">
+        <is>
+          <t>Among the 900 residents of Aimeville, there are 195 who own a diamond
+ring, 367 who own a set of golf clubs, and 562 who own a garden spade.
+In addition, each of the 900 residents owns a bag of candy hearts.
+There are 437 residents who own exactly two of these things, and 234
+residents who own exactly three of these things. Find the number of
+residents of Aimeville who own all four of these things.</t>
+        </is>
+      </c>
+      <c r="G118" s="1" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="H118" s="1" t="inlineStr"/>
+    </row>
+    <row r="119" ht="72" customHeight="1">
+      <c r="A119" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="1" t="inlineStr">
         <is>
           <t>COMB_H_003</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t>AIME</t>
         </is>
       </c>
-      <c r="D114" s="1" t="inlineStr">
+      <c r="D119" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E114" s="1" t="inlineStr">
+      <c r="E119" s="1" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F114" s="1" t="inlineStr">
-        <is>
-          <t>8. From an unlimited supply of 1-cent coins, 10-cent coins, and
-25-cent coins, Silas wants to find a collection of coins that has a
-total value of N cents, where N is a positive integer. He uses the so-
-called greedy algorithm, successively choosing the coin of greatest
-value that does not cause the value of his collection to exceed N. For
+      <c r="F119" s="1" t="inlineStr">
+        <is>
+          <t>A list of positive integers has the following properties: the sum of
+the items in the list is 30; the unique mode of the list is 9; the
+median of the list is a positive integer that does not appear in the
+list itself. Find the sum of the squares of all the items in the list.</t>
+        </is>
+      </c>
+      <c r="G119" s="1" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="H119" s="1" t="inlineStr"/>
+    </row>
+    <row r="120" ht="72" customHeight="1">
+      <c r="A120" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="1" t="inlineStr">
+        <is>
+          <t>COMB_H_004</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="inlineStr">
+        <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D120" s="1" t="inlineStr">
+        <is>
+          <t>Combinatorics</t>
+        </is>
+      </c>
+      <c r="E120" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F120" s="1" t="inlineStr">
+        <is>
+          <t>Alice chooses a set A of positive integers. Then Bob lists all finite
+nonempty sets B of positive integers with the property that the
+maximum element of B belongs to A. Bob's list has 2024 sets. Find the
+sum of the elements of A.</t>
+        </is>
+      </c>
+      <c r="G120" s="1" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="H120" s="1" t="inlineStr"/>
+    </row>
+    <row r="121" ht="108" customHeight="1">
+      <c r="A121" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="1" t="inlineStr">
+        <is>
+          <t>COMB_H_005</t>
+        </is>
+      </c>
+      <c r="C121" s="1" t="inlineStr">
+        <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D121" s="1" t="inlineStr">
+        <is>
+          <t>Combinatorics</t>
+        </is>
+      </c>
+      <c r="E121" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F121" s="1" t="inlineStr">
+        <is>
+          <t>There is a collection of 25 indistinguishable white chips and 25
+indistinguishable black chips. Find the number of ways to place some
+of these chips in a 5x5 grid such that: each cell contains at most one
+chip; all chips in the same row and all chips in the same column have
+the same color; and any additional chip placed on the grid would
+violate one or more of the previous two conditions.</t>
+        </is>
+      </c>
+      <c r="G121" s="1" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="H121" s="1" t="inlineStr"/>
+    </row>
+    <row r="122" ht="144" customHeight="1">
+      <c r="A122" s="1" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="1" t="inlineStr">
+        <is>
+          <t>COMB_H_006</t>
+        </is>
+      </c>
+      <c r="C122" s="1" t="inlineStr">
+        <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D122" s="1" t="inlineStr">
+        <is>
+          <t>Combinatorics</t>
+        </is>
+      </c>
+      <c r="E122" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F122" s="1" t="inlineStr">
+        <is>
+          <t>The 9 members of a baseball team went to an ice-cream parlor after
+their game. Each player had a single scoop cone of chocolate, vanilla,
+or strawberry ice cream. At least one player chose each flavor, and
+the number of players who chose chocolate was greater than the number
+of players who chose vanilla, which was greater than the number of
+players who chose strawberry. Let N be the number of different
+assignments of flavors to players that meet these conditions. Find the
+remainder when N is divided by 1000.</t>
+        </is>
+      </c>
+      <c r="G122" s="1" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H122" s="1" t="inlineStr"/>
+    </row>
+    <row r="123" ht="270" customHeight="1">
+      <c r="A123" s="1" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="1" t="inlineStr">
+        <is>
+          <t>COMB_H_007</t>
+        </is>
+      </c>
+      <c r="C123" s="1" t="inlineStr">
+        <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D123" s="1" t="inlineStr">
+        <is>
+          <t>Combinatorics</t>
+        </is>
+      </c>
+      <c r="E123" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F123" s="1" t="inlineStr">
+        <is>
+          <t>From an unlimited supply of 1-cent coins, 10-cent coins, and 25-cent
+coins, Silas wants to find a collection of coins that has a total
+value of N cents, where N is a positive integer. He uses the so-called
+greedy algorithm, successively choosing the coin of greatest value
+that does not cause the value of his collection to exceed N. For
 example, to get 42 cents, Silas will choose a 25-cent coin, then a
 10-cent coin, then 7 1-cent coins. However, this collection of 9 coins
 uses more coins than necessary to get a total of 42 cents; indeed,
-choosing 410-cent coins and 21-cent coins achieves the same total
+choosing 4 10-cent coins and 2 1-cent coins achieves the same total
 value with only 6 coins. In general, the greedy algorithm succeeds for
-a given N if no other collection of 1- cent, 10-cent, and 25-cent
-coins gives a total value of N cents using strictly fewer coins than
-the collection given by the greedy algorithm. Find the number of
-values of N between 1 and 1000 inclusive for which the greedy
-algorithm succeeds.</t>
-        </is>
-      </c>
-      <c r="G114" s="1" t="inlineStr">
+a given N if no other collection of 1-cent, 10-cent, and 25-cent coins
+gives a total value of N cents using strictly fewer coins than the
+collection given by the greedy algorithm. Find the number of values of
+N between 1 and 1000 inclusive for which the greedy algorithm
+succeeds.</t>
+        </is>
+      </c>
+      <c r="G123" s="1" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr"/>
-    </row>
-    <row r="115" ht="108" customHeight="1">
-      <c r="A115" s="1" t="n">
-        <v>114</v>
-      </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>COMB_H_004</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
+      <c r="H123" s="1" t="inlineStr"/>
+    </row>
+    <row r="124" ht="72" customHeight="1">
+      <c r="A124" s="1" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="1" t="inlineStr">
+        <is>
+          <t>COMB_H_008</t>
+        </is>
+      </c>
+      <c r="C124" s="1" t="inlineStr">
         <is>
           <t>AIME</t>
         </is>
       </c>
-      <c r="D115" s="1" t="inlineStr">
+      <c r="D124" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E115" s="1" t="inlineStr">
+      <c r="E124" s="1" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F115" s="1" t="inlineStr">
-        <is>
-          <t>1. Among the 900 residents of Aimeville, there are 195 who own a
-diamond ring, 367 who own a set of golf clubs, and 562 who own a
-garden spade. In addition, each of the 900 residents owns a bag of
-candy hearts. There are 437 residents who own exactly two of these
-things, and 234 residents who own exactly three of these things. Find
-the number of residents of Aimeville who own all four of these things.</t>
-        </is>
-      </c>
-      <c r="G115" s="1" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr"/>
-    </row>
-    <row r="116" ht="72" customHeight="1">
-      <c r="A116" s="1" t="n">
-        <v>115</v>
-      </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>COMB_H_005</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
+      <c r="F124" s="1" t="inlineStr">
+        <is>
+          <t>Sixteen chairs are arranged in a row. Eight people each select a chair
+in which to sit so that no person sits next to two other people. Let N
+be the number of subsets of 16 chairs that could be selected. Find the
+remainder when N is divided by 1000.</t>
+        </is>
+      </c>
+      <c r="G124" s="1" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="H124" s="1" t="inlineStr"/>
+    </row>
+    <row r="125" ht="54" customHeight="1">
+      <c r="A125" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="1" t="inlineStr">
+        <is>
+          <t>COMB_H_009</t>
+        </is>
+      </c>
+      <c r="C125" s="1" t="inlineStr">
         <is>
           <t>AIME</t>
         </is>
       </c>
-      <c r="D116" s="1" t="inlineStr">
+      <c r="D125" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E116" s="1" t="inlineStr">
+      <c r="E125" s="1" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F116" s="1" t="inlineStr">
-        <is>
-          <t>10. Sixteen chairs are arranged in a row. Eight people each select a
-chair in which to sit so that no person sits next to two other people.
-Let N be the number of subsets of 16 chairs that could be selected.
-Find the remainder when N is divided by 1000.</t>
-        </is>
-      </c>
-      <c r="G116" s="1" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr"/>
-    </row>
-    <row r="117" ht="54" customHeight="1">
-      <c r="A117" s="1" t="n">
-        <v>116</v>
-      </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>COMB_H_006</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
+      <c r="F125" s="1" t="inlineStr">
+        <is>
+          <t>Let S be the set of vertices of a regular 24-gon. Find the number of
+ways to draw 12 segments of equal lengths so that each vertex in S is
+an endpoint of exactly one of the 12 segments.</t>
+        </is>
+      </c>
+      <c r="G125" s="1" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="H125" s="1" t="inlineStr"/>
+    </row>
+    <row r="126" ht="90" customHeight="1">
+      <c r="A126" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="1" t="inlineStr">
+        <is>
+          <t>COMB_H_010</t>
+        </is>
+      </c>
+      <c r="C126" s="1" t="inlineStr">
+        <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D126" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E117" s="1" t="inlineStr">
+      <c r="E126" s="1" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F117" s="1" t="inlineStr">
-        <is>
-          <t>23 people attend a party. Each person shakes hands with at least two
-other people. What is the minimum possible number of handshakes?</t>
-        </is>
-      </c>
-      <c r="G117" s="1" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>If each person shakes hands with exactly two other people, then there will be (23 · 2/2) =
-23 handshakes. To achieve 23 handshakes, we arrange the participants in a circle. Each
-person shakes hands with the two people next to him or her.</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="90" customHeight="1">
-      <c r="A118" s="1" t="n">
-        <v>117</v>
-      </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>COMB_H_007</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
+      <c r="F126" s="1" t="inlineStr">
+        <is>
+          <t>Find the number of positive integer palindromes written in base 10,
+with no zero digits, and whose digits add up to 13. For example, 42124
+has these properties. Recall that a palindrome is a number whose
+representation reads the same from left to right as from right to
+left.</t>
+        </is>
+      </c>
+      <c r="G126" s="1" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="H126" s="1" t="inlineStr"/>
+    </row>
+    <row r="127" ht="54" customHeight="1">
+      <c r="A127" s="1" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="1" t="inlineStr">
+        <is>
+          <t>COMB_H_011</t>
+        </is>
+      </c>
+      <c r="C127" s="1" t="inlineStr">
+        <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D127" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E118" s="1" t="inlineStr">
+      <c r="E127" s="1" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F118" s="1" t="inlineStr">
-        <is>
-          <t>A Senate committee has 5 Democrats and 5 Republicans. In how many ways
-can they sit around a circular table if each member sits next to two
-members of the other party? (Two seatings are the same if one is a
-rotation of the other.)</t>
-        </is>
-      </c>
-      <c r="G118" s="1" t="inlineStr">
-        <is>
-          <t>2,\!880</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>The only way that the Senators can be seated is if the seats alternate by party. Fix the
-rotation by placing the youngest Democrat in the top seat, so that we have removed the
-overcounting of rotations of the same arrangement. Now there are 4! ways to place the
-remaining Democrats in the other Democratic seats, and 5! ways to place the Republicans in
-the Republican seats, for a total of 5! × 4! = 2,880 arrangements.</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="162" customHeight="1">
-      <c r="A119" s="1" t="n">
-        <v>118</v>
-      </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>COMB_H_008</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D119" s="1" t="inlineStr">
+      <c r="F127" s="1" t="inlineStr">
+        <is>
+          <t>Find the number of functions pi mapping the set A = {1,2,3,4,5,6} onto
+A such that for every a in A, applying pi to a six times in a row
+(pi(pi(pi(pi(pi(pi(a))))))) equals a.</t>
+        </is>
+      </c>
+      <c r="G127" s="1" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="H127" s="1" t="inlineStr"/>
+    </row>
+    <row r="128" ht="126" customHeight="1">
+      <c r="A128" s="1" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="1" t="inlineStr">
+        <is>
+          <t>COMB_H_012</t>
+        </is>
+      </c>
+      <c r="C128" s="1" t="inlineStr">
+        <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D128" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E119" s="1" t="inlineStr">
+      <c r="E128" s="1" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F119" s="1" t="inlineStr">
-        <is>
-          <t>A bakery sells three kinds of rolls. How many different combinations
-of rolls could Jack purchase if he buys a total of six rolls and
-includes at least one of each kind?</t>
-        </is>
-      </c>
-      <c r="G119" s="1" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>We don't have to worry about three of the rolls since there will be one of each kind. Now
-we look at the possible cases for the remaining three rolls. \emphCase 1: The remaining
-three rolls are one of each kind, for which there is only \emph1 combination. \emphCase 2:
-The remaining three rolls are all the same kind. Since there are three different kinds of
-rolls, there are \emph3 possibilities for this case. \emphCase 3: The remaining three
-rolls are two of one kind and one of another kind. We have three choices for the rolls we
-have two of, which leaves two choices for the rolls we have one of, and then one choice
-for the kind of roll we don't have. So there are 3!=\emph6 possibilities for this case. In
-total, we have 1+3+6=10 possible combinations of rolls that Jack could purchase.</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="198" customHeight="1">
-      <c r="A120" s="1" t="n">
-        <v>119</v>
-      </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>COMB_H_009</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
+      <c r="F128" s="1" t="inlineStr">
+        <is>
+          <t>The integers from 1 to 64 are placed in some order into an 8x8 grid of
+cells with one number in each cell. Let a_(i,j) be the number placed
+in the cell in row i and column j, and let M be the sum of the
+absolute differences between adjacent cells. That is, M = the sum,
+over i = 1 to 8 and j = 1 to 7, of (|a_(i,j+1) - a_(i,j)| + |a_(j+1,i)
+- a_(j,i)|). Find the remainder when the maximum possible value of M
+is divided by 1000.</t>
+        </is>
+      </c>
+      <c r="G128" s="1" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="H128" s="1" t="inlineStr"/>
+    </row>
+    <row r="129" ht="108" customHeight="1">
+      <c r="A129" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="1" t="inlineStr">
+        <is>
+          <t>COMB_H_013</t>
+        </is>
+      </c>
+      <c r="C129" s="1" t="inlineStr">
+        <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D129" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E120" s="1" t="inlineStr">
+      <c r="E129" s="1" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F120" s="1" t="inlineStr">
-        <is>
-          <t>A bored student walks down a hall that contains a row of closed
-lockers, numbered 1 to 1024. He opens the locker numbered 1, and then
-alternates between skipping and opening each locker thereafter. When
-he reaches the end of the hall, the student turns around and starts
-back. He opens the first closed locker he encounters, and then
-alternates between skipping and opening each closed locker thereafter.
-The student continues wandering back and forth in this manner until
-every locker is open. What is the number of the last locker he opens?</t>
-        </is>
-      </c>
-      <c r="G120" s="1" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>On his first pass, he opens all of the odd lockers. So there are only even lockers closed.
-Then he opens the lockers that are multiples of 4, leaving only lockers 2 \pmod8 and 6
-\pmod8. Then he goes ahead and opens all lockers 2 \pmod 8, leaving lockers either 6 \pmod
-16 or 14 \pmod 16. He then goes ahead and opens all lockers 14 \pmod 16, leaving the
-lockers either 6 \pmod 32 or 22 \pmod 32. He then goes ahead and opens all lockers 6 \pmod
-32, leaving 22 \pmod 64 or 54 \pmod 64. He then opens 54 \pmod 64, leaving 22 \pmod 128 or
-86 \pmod 128. He then opens 22 \pmod 128 and leaves 86 \pmod 256 and 214 \pmod 256. He
-then opens all 214 \pmod 256, so we have 86 \pmod 512 and 342 \pmod 512, leaving lockers
-86, 342, 598, and 854, and he is at where he started again. He then opens 86 and 598, and
-then goes back and opens locker number 854, leaving locker number 342 untouched. He opens
-that locker.</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="414" customHeight="1">
-      <c r="A121" s="1" t="n">
-        <v>120</v>
-      </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>COMB_H_010</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>Hendrycks</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
+      <c r="F129" s="1" t="inlineStr">
+        <is>
+          <t>For each nonnegative integer r less than 502, define S_r = the sum,
+over m ≥ 0, of C(10000, 502m + r), where C(10000, n) is defined to be
+0 when n &gt; 10,000. That is, S_r is the sum of all the binomial
+coefficients of the form C(10000, k) for which 0 ≤ k ≤ 10,000 and k -
+r is a multiple of 502. Find the number of integers in the list S_0,
+S_1, S_2, ..., S_501 that are multiples of the prime number 503.</t>
+        </is>
+      </c>
+      <c r="G129" s="1" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="H129" s="1" t="inlineStr"/>
+    </row>
+    <row r="130" ht="108" customHeight="1">
+      <c r="A130" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="1" t="inlineStr">
+        <is>
+          <t>COMB_H_014</t>
+        </is>
+      </c>
+      <c r="C130" s="1" t="inlineStr">
+        <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D130" s="1" t="inlineStr">
         <is>
           <t>Combinatorics</t>
         </is>
       </c>
-      <c r="E121" s="1" t="inlineStr">
+      <c r="E130" s="1" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="F121" s="1" t="inlineStr">
-        <is>
-          <t>A cube is painted so that one side is blue, two sides are red, and
-three sides are green. How many different such cubes can be painted?
-Two cubes are considered the same if one cube can be rotated in any
-way to match the second cube.</t>
-        </is>
-      </c>
-      <c r="G121" s="1" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>Orient the cube so that the blue face is on top. At least one red face must be adjacent to
-the blue face, and the other red face can be in one of 3 distinct positions relative to
-these two (see figure). The green faces are determined by the placement of the red and
-blue faces. [asy] import three; size(250); defaultpen(linewidth(0.7)); settings.prc=false;
-settings.render=0; currentprojection=orthographic(30,-20,15); void drawCube (picture
-pic=currentpicture, real a, real b, real c) draw(pic,shift(a,b,c)*surface((0,0,1)--
-(0,1,1)--(1,1,1)--(1,0,1)--cycle),white,black+linewidth(1.0),nolight); draw(pic,shift(a,b,
-c)*surface((1,0,0)--(1,0,1)--(1,1,1)--(1,1,0)--cycle),white,black+linewidth(1.0),nolight);
-draw(pic,shift(a,b,c)*surface((0,0,0)--(1,0,0)--(1,0,1)--(0,0,1)--
-cycle),white,black+linewidth(1.0),nolight); drawCube(0,0,0);
-label(scale(2.5)*project("B",Y,-X),(1/2,1/2,1));
-label(scale(2.5)*project("R",Y,Z),(1,1/2,1/2));
-label(scale(2.5)*project("R",X,Z),(1/2,0,1/2)); picture pic1; drawCube(pic1,0,0,0);
-label(pic1,scale(2.5)*project("B",Y,-X),(1/2,1/2,1));
-label(pic1,scale(2.5)*project("R",Y,Z),(1,1/2,1/2));
-label(pic1,scale(2.5)*project("R",Y,Z),(0,1/2,1/2));
-draw(pic1,(0,0,0)--(0,1,0)--(0,1,1),linetype("2 3"));
-draw(pic1,(0,1,0)--(1,1,0),linetype("2 3")); add(shift((1,1.5,0))*pic1); picture pic2;
-drawCube(pic2,0,0,0); label(pic2,scale(2.5)*project("B",Y,-X),(1/2,1/2,1));
-label(pic2,scale(2.5)*project("R",Y,Z),(1,1/2,1/2));
-label(pic2,scale(2.5)*project("R",Y,-X),(1/2,1/2,0));
-draw(pic2,(0,0,0)--(0,1,0)--(0,1,1),linetype("2 3"));
-draw(pic2,(0,1,0)--(1,1,0),linetype("2 3")); add(shift((2,3,0))*pic2);[/asy]</t>
-        </is>
-      </c>
+      <c r="F130" s="1" t="inlineStr">
+        <is>
+          <t>Call finite sets of integers S and T cousins if: S and T have the same
+number of elements; S and T are disjoint; and the elements of S can be
+paired with the elements of T so that the elements in each pair differ
+by exactly 1. For example, {1,2,5} and {0,3,4} are cousins. Suppose
+that the set S has exactly 4040 cousins. Find the least number of
+elements the set S can have.</t>
+        </is>
+      </c>
+      <c r="G130" s="1" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="H130" s="1" t="inlineStr"/>
+    </row>
+    <row r="131" ht="90" customHeight="1">
+      <c r="A131" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="1" t="inlineStr">
+        <is>
+          <t>COMB_H_015</t>
+        </is>
+      </c>
+      <c r="C131" s="1" t="inlineStr">
+        <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D131" s="1" t="inlineStr">
+        <is>
+          <t>Combinatorics</t>
+        </is>
+      </c>
+      <c r="E131" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F131" s="1" t="inlineStr">
+        <is>
+          <t>For integers a and b, let a○b = a - b if a is odd and b is even, and
+a○b = a + b otherwise. Find the number of sequences a_1, a_2, a_3,
+..., a_n of positive integers such that a_1 + a_2 + a_3 + ... + a_n =
+12 and a_1○a_2○a_3○...○a_n = 0, where the operations are performed
+from left to right; that is, a_1○a_2○a_3 means (a_1○a_2)○a_3.</t>
+        </is>
+      </c>
+      <c r="G131" s="1" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="H131" s="1" t="inlineStr"/>
+    </row>
+    <row r="132" ht="90" customHeight="1">
+      <c r="A132" s="1" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="1" t="inlineStr">
+        <is>
+          <t>COMB_H_016</t>
+        </is>
+      </c>
+      <c r="C132" s="1" t="inlineStr">
+        <is>
+          <t>AIME</t>
+        </is>
+      </c>
+      <c r="D132" s="1" t="inlineStr">
+        <is>
+          <t>Combinatorics</t>
+        </is>
+      </c>
+      <c r="E132" s="1" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="F132" s="1" t="inlineStr">
+        <is>
+          <t>Find the number of ordered 7-tuples (a_1, a_2, a_3, ..., a_7) having
+the following properties: a_k is in {1,2,3} for all k; a_1 + a_2 + a_3
++ a_4 + a_5 + a_6 + a_7 is a multiple of 3; a_1*a_2*a_4 + a_2*a_3*a_5
++ a_3*a_4*a_6 + a_4*a_5*a_7 + a_5*a_6*a_1 + a_6*a_7*a_2 + a_7*a_1*a_3
+is a multiple of 3.</t>
+        </is>
+      </c>
+      <c r="G132" s="1" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="H132" s="1" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H121"/>
+  <autoFilter ref="A1:H132"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>